--- a/docs/data/jp/xlsx/6797.xlsx
+++ b/docs/data/jp/xlsx/6797.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC164"/>
+  <dimension ref="A1:AC171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4185,10 +4188,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>1174</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4223,7 +4228,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>12844000</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5422,7 +5429,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5668,3493 +5675,3901 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>2847.399</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>2386.377</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>4936.502</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>1694.583</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>2159.823</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>2865.071</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>4634.897</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>1271.428</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>2753.363</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>3001.748</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>5289.589</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>1642.393</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>4936.502</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>4634.897</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>5289.589</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>774.585</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>951.471</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>2929.092</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>746.55</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>1026.485</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>1416.347</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>2718.542</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>545.117</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>1046.841</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>1106.557</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>2292.738</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>766.7670000000001</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>2929.092</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>2718.542</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>2292.738</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>774.543</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>725.0359999999999</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>818.567</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>716.686</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>712.561</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>738.044</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>988.535</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>768.318</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>822.4059999999999</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>750.936</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>900.235</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>774.28</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>818.567</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>988.535</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>900.235</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>Operating Income</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>226.435</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>2110.524</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>29.863</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>313.925</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>678.302</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>1730.007</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>-223.201</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>224.435</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>355.621</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>1392.503</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>-7.512</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>2110.524</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>1730.007</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>1392.503</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>배당금수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>0.32</v>
+        <v>774.543</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>13.36</v>
+        <v>725.0359999999999</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>0</v>
+        <v>818.567</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>12.702</v>
+        <v>716.686</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>0.35</v>
+        <v>712.561</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>16.558</v>
+        <v>738.044</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>0</v>
+        <v>988.535</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>14.505</v>
+        <v>768.318</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>0</v>
+        <v>822.4059999999999</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>19.807</v>
+        <v>750.936</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>0</v>
+        <v>900.235</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>22.734</v>
+        <v>774.28</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>0</v>
+        <v>818.567</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>0</v>
+        <v>988.535</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>0</v>
+        <v>900.235</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>부동산 임대료</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>23.917</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>30.456</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>31.056</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>30.858</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>30.771</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>30.771</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>30.772</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>30.808</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>30.767</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>28.014</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>28.017</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>28.002</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>31.056</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>30.772</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>28.017</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>226.435</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>2110.524</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>29.863</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>313.925</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>678.302</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>1730.007</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>-223.201</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>224.435</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>355.621</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>1392.503</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>-7.512</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>2110.524</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>1730.007</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>1392.503</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>보상금 수취</t>
-        </is>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>0.249</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>0.249</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>0.462</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>10.333</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>10.333</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>-0.289</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>0.589</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>Haizaishobunshunyu NOI</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>1.866</v>
+        <v>0.32</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>2.175</v>
+        <v>13.36</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>6.063</v>
+        <v>12.702</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>4.67</v>
+        <v>0.35</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>7.036</v>
+        <v>16.558</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>4.441</v>
+        <v>0</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>3.802</v>
+        <v>14.505</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>3.379</v>
+        <v>0</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>2.309</v>
+        <v>19.807</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>4.851</v>
+        <v>0</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>4.871</v>
+        <v>22.734</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>4.441</v>
+        <v>0</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>4.851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>부동산 임대료</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>-2.963</v>
+        <v>23.917</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>2.763</v>
+        <v>30.456</v>
+      </c>
+      <c r="E88" s="22" t="n">
+        <v>31.056</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>10.3</v>
+        <v>30.858</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>-8.019</v>
+        <v>30.771</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>4.158</v>
+        <v>30.771</v>
+      </c>
+      <c r="I88" s="22" t="n">
+        <v>30.772</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>1.391</v>
+        <v>30.808</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>4.319</v>
+        <v>30.767</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>3.271</v>
+        <v>28.014</v>
+      </c>
+      <c r="M88" s="22" t="n">
+        <v>28.017</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>11.59</v>
+        <v>28.002</v>
+      </c>
+      <c r="V88" s="22" t="n">
+        <v>31.056</v>
+      </c>
+      <c r="W88" s="22" t="n">
+        <v>30.772</v>
+      </c>
+      <c r="X88" s="22" t="n">
+        <v>28.017</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="C89" s="22" t="n">
-        <v>27.053</v>
+          <t>보상금 수취</t>
+        </is>
       </c>
       <c r="D89" s="22" t="n">
-        <v>49.53</v>
+        <v>0.575</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>43.289</v>
-      </c>
-      <c r="F89" s="22" t="n">
-        <v>70.258</v>
-      </c>
-      <c r="G89" s="22" t="n">
-        <v>29.443</v>
+        <v>0.249</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>58.688</v>
+        <v>0.166</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>37.811</v>
-      </c>
-      <c r="J89" s="22" t="n">
-        <v>60.84</v>
-      </c>
-      <c r="K89" s="22" t="n">
-        <v>38.808</v>
+        <v>0.386</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>53.109</v>
+        <v>0</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>44.285</v>
-      </c>
-      <c r="N89" s="22" t="n">
-        <v>67.419</v>
+        <v>0.462</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>43.289</v>
+        <v>0.249</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>37.811</v>
+        <v>0.386</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>44.285</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>지급보증료</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>5.716</v>
+        <v>0</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>1.962</v>
+        <v>0.2</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>3.751</v>
+        <v>0</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>2.636</v>
+        <v>10.333</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>3.988</v>
+        <v>0.126</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>0.737</v>
+        <v>0</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>4.452</v>
+        <v>0.348</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>5.875</v>
+        <v>10.333</v>
       </c>
       <c r="K90" s="22" t="n">
-        <v>6.967</v>
+        <v>0.289</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>3.148</v>
+        <v>-0.289</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>4.088</v>
+        <v>0.589</v>
       </c>
       <c r="N90" s="22" t="n">
-        <v>2.802</v>
+        <v>0.221</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>3.751</v>
+        <v>0</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>4.452</v>
+        <v>0.348</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>4.088</v>
+        <v>0.589</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
+          <t>Haizaishobunshunyu NOI</t>
+        </is>
+      </c>
+      <c r="C91" s="22" t="n">
+        <v>1.866</v>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="E91" s="22" t="n">
+        <v>2.41</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>2.172</v>
+        <v>6.063</v>
+      </c>
+      <c r="G91" s="22" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="H91" s="22" t="n">
+        <v>7.036</v>
+      </c>
+      <c r="I91" s="22" t="n">
+        <v>4.441</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>1.548</v>
+        <v>3.802</v>
+      </c>
+      <c r="K91" s="22" t="n">
+        <v>3.379</v>
+      </c>
+      <c r="L91" s="22" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="M91" s="22" t="n">
+        <v>4.851</v>
       </c>
       <c r="N91" s="22" t="n">
-        <v>0.556</v>
+        <v>4.871</v>
+      </c>
+      <c r="V91" s="22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="W91" s="22" t="n">
+        <v>4.441</v>
+      </c>
+      <c r="X91" s="22" t="n">
+        <v>4.851</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>Rent Expenses On Real Estates NOE</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>28.229</v>
+        <v>-2.963</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>28.397</v>
-      </c>
-      <c r="E92" s="22" t="n">
-        <v>28.48</v>
+        <v>2.763</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>28.582</v>
+        <v>10.3</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>29.353</v>
+        <v>-8.019</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>28.552</v>
-      </c>
-      <c r="I92" s="22" t="n">
-        <v>28.669</v>
+        <v>4.158</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>28.741</v>
+        <v>1.391</v>
       </c>
       <c r="K92" s="22" t="n">
-        <v>29.145</v>
+        <v>4.319</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>29.373</v>
-      </c>
-      <c r="M92" s="22" t="n">
-        <v>28.509</v>
+        <v>3.271</v>
       </c>
       <c r="N92" s="22" t="n">
-        <v>28.468</v>
-      </c>
-      <c r="V92" s="22" t="n">
-        <v>28.48</v>
-      </c>
-      <c r="W92" s="22" t="n">
-        <v>28.669</v>
-      </c>
-      <c r="X92" s="22" t="n">
-        <v>28.509</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>Accident Related Expenses NOE</t>
-        </is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="n">
+        <v>27.053</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>0</v>
+        <v>49.53</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>0.252</v>
+        <v>43.289</v>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>70.258</v>
+      </c>
+      <c r="G93" s="22" t="n">
+        <v>29.443</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>0</v>
+        <v>58.688</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>0.962</v>
+        <v>37.811</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="K93" s="22" t="n">
+        <v>38.808</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>0</v>
+        <v>53.109</v>
       </c>
       <c r="M93" s="22" t="n">
-        <v>1.119</v>
+        <v>44.285</v>
+      </c>
+      <c r="N93" s="22" t="n">
+        <v>67.419</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>0.252</v>
+        <v>43.289</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>0.962</v>
+        <v>37.811</v>
       </c>
       <c r="X93" s="22" t="n">
-        <v>1.119</v>
+        <v>44.285</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
+          <t>지급보증료</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n">
+        <v>5.716</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>0</v>
+        <v>1.962</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>0</v>
+        <v>3.751</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>0</v>
+        <v>2.636</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>20.582</v>
+        <v>3.988</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>-16.223</v>
+        <v>0.737</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>12.664</v>
+        <v>4.452</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>8.413</v>
+        <v>5.875</v>
       </c>
       <c r="K94" s="22" t="n">
-        <v>1.602</v>
+        <v>6.967</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>-8.757</v>
+        <v>3.148</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>7.468</v>
+        <v>4.088</v>
       </c>
       <c r="N94" s="22" t="n">
-        <v>0</v>
+        <v>2.802</v>
       </c>
       <c r="V94" s="22" t="n">
-        <v>0</v>
+        <v>3.751</v>
       </c>
       <c r="W94" s="22" t="n">
-        <v>12.664</v>
+        <v>4.452</v>
       </c>
       <c r="X94" s="22" t="n">
-        <v>7.468</v>
+        <v>4.088</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C95" s="22" t="n">
-        <v>13.904</v>
-      </c>
-      <c r="D95" s="22" t="n">
-        <v>3.609</v>
+          <t>고정자산 제각손실</t>
+        </is>
       </c>
       <c r="F95" s="22" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="G95" s="22" t="n">
-        <v>5.578</v>
-      </c>
-      <c r="H95" s="22" t="n">
-        <v>1.976</v>
+        <v>2.172</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K95" s="22" t="n">
-        <v>2.886</v>
-      </c>
-      <c r="L95" s="22" t="n">
-        <v>0.453</v>
+        <v>1.548</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>0.015</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>Rent Expenses On Real Estates NOE</t>
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>48.973</v>
+        <v>28.229</v>
       </c>
       <c r="D96" s="22" t="n">
-        <v>33.967</v>
+        <v>28.397</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>38.022</v>
+        <v>28.48</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>34.15</v>
+        <v>28.582</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>60</v>
+        <v>29.353</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>15.043</v>
+        <v>28.552</v>
       </c>
       <c r="I96" s="22" t="n">
-        <v>56.255</v>
+        <v>28.669</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>44.589</v>
+        <v>28.741</v>
       </c>
       <c r="K96" s="22" t="n">
-        <v>39.051</v>
+        <v>29.145</v>
       </c>
       <c r="L96" s="22" t="n">
-        <v>24.217</v>
+        <v>29.373</v>
       </c>
       <c r="M96" s="22" t="n">
-        <v>44.502</v>
+        <v>28.509</v>
       </c>
       <c r="N96" s="22" t="n">
-        <v>31.842</v>
+        <v>28.468</v>
       </c>
       <c r="V96" s="22" t="n">
-        <v>38.022</v>
+        <v>28.48</v>
       </c>
       <c r="W96" s="22" t="n">
-        <v>56.255</v>
+        <v>28.669</v>
       </c>
       <c r="X96" s="22" t="n">
-        <v>44.502</v>
+        <v>28.509</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>경상이익(손실)</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="n">
-        <v>-21.876</v>
-      </c>
-      <c r="D97" s="12" t="n">
-        <v>241.997</v>
-      </c>
-      <c r="E97" s="12" t="n">
-        <v>2115.791</v>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>65.971</v>
-      </c>
-      <c r="G97" s="12" t="n">
-        <v>283.368</v>
-      </c>
-      <c r="H97" s="12" t="n">
-        <v>721.947</v>
-      </c>
-      <c r="I97" s="12" t="n">
-        <v>1711.562</v>
-      </c>
-      <c r="J97" s="12" t="n">
-        <v>-206.95</v>
-      </c>
-      <c r="K97" s="12" t="n">
-        <v>224.191</v>
-      </c>
-      <c r="L97" s="12" t="n">
-        <v>384.514</v>
-      </c>
-      <c r="M97" s="12" t="n">
-        <v>1392.286</v>
-      </c>
-      <c r="N97" s="12" t="n">
-        <v>28.064</v>
-      </c>
-      <c r="V97" s="12" t="n">
-        <v>2115.791</v>
-      </c>
-      <c r="W97" s="12" t="n">
-        <v>1711.562</v>
-      </c>
-      <c r="X97" s="12" t="n">
-        <v>1392.286</v>
+      <c r="A97" s="20" t="inlineStr">
+        <is>
+          <t>Accident Related Expenses NOE</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="H97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="22" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="22" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="V97" s="22" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="W97" s="22" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="X97" s="22" t="n">
+        <v>1.119</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각이익</t>
-        </is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="D98" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="E98" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="F98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="22" t="n">
+        <v>20.582</v>
+      </c>
       <c r="H98" s="22" t="n">
-        <v>0</v>
+        <v>-16.223</v>
       </c>
       <c r="I98" s="22" t="n">
-        <v>0</v>
+        <v>12.664</v>
+      </c>
+      <c r="J98" s="22" t="n">
+        <v>8.413</v>
+      </c>
+      <c r="K98" s="22" t="n">
+        <v>1.602</v>
       </c>
       <c r="L98" s="22" t="n">
-        <v>0.35</v>
+        <v>-8.757</v>
       </c>
       <c r="M98" s="22" t="n">
+        <v>7.468</v>
+      </c>
+      <c r="N98" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V98" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W98" s="22" t="n">
-        <v>0</v>
+        <v>12.664</v>
       </c>
       <c r="X98" s="22" t="n">
-        <v>0</v>
+        <v>7.468</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각이익</t>
-        </is>
-      </c>
-      <c r="E99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="22" t="n">
-        <v>28.515</v>
-      </c>
-      <c r="M99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" s="22" t="n">
-        <v>28.515</v>
-      </c>
-      <c r="X99" s="22" t="n">
-        <v>0</v>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="n">
+        <v>13.904</v>
+      </c>
+      <c r="D99" s="22" t="n">
+        <v>3.609</v>
+      </c>
+      <c r="F99" s="22" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="G99" s="22" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="H99" s="22" t="n">
+        <v>1.976</v>
+      </c>
+      <c r="J99" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K99" s="22" t="n">
+        <v>2.886</v>
+      </c>
+      <c r="L99" s="22" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="N99" s="22" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>특별이익 합계</t>
-        </is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C100" s="22" t="n">
+        <v>48.973</v>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>33.967</v>
       </c>
       <c r="E100" s="22" t="n">
+        <v>38.022</v>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="G100" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="H100" s="22" t="n">
+        <v>15.043</v>
+      </c>
+      <c r="I100" s="22" t="n">
+        <v>56.255</v>
+      </c>
+      <c r="J100" s="22" t="n">
+        <v>44.589</v>
+      </c>
+      <c r="K100" s="22" t="n">
+        <v>39.051</v>
+      </c>
+      <c r="L100" s="22" t="n">
+        <v>24.217</v>
+      </c>
+      <c r="M100" s="22" t="n">
+        <v>44.502</v>
+      </c>
+      <c r="N100" s="22" t="n">
+        <v>31.842</v>
+      </c>
+      <c r="V100" s="22" t="n">
+        <v>38.022</v>
+      </c>
+      <c r="W100" s="22" t="n">
+        <v>56.255</v>
+      </c>
+      <c r="X100" s="22" t="n">
+        <v>44.502</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>경상이익(손실)</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>-21.876</v>
+      </c>
+      <c r="D101" s="12" t="n">
+        <v>241.997</v>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>2115.791</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>65.971</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>283.368</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>721.947</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>1711.562</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>-206.95</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>224.191</v>
+      </c>
+      <c r="L101" s="12" t="n">
+        <v>384.514</v>
+      </c>
+      <c r="M101" s="12" t="n">
+        <v>1392.286</v>
+      </c>
+      <c r="N101" s="12" t="n">
+        <v>28.064</v>
+      </c>
+      <c r="V101" s="12" t="n">
+        <v>2115.791</v>
+      </c>
+      <c r="W101" s="12" t="n">
+        <v>1711.562</v>
+      </c>
+      <c r="X101" s="12" t="n">
+        <v>1392.286</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G102" s="17">
+        <f>IF(OR(G101="",C101=""),"",IF(C101&lt;=0,"",IFERROR(G101/C101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H102" s="17">
+        <f>IF(OR(H101="",D101=""),"",IF(D101&lt;=0,"",IFERROR(H101/D101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I102" s="17">
+        <f>IF(OR(I101="",E101=""),"",IF(E101&lt;=0,"",IFERROR(I101/E101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J102" s="17">
+        <f>IF(OR(J101="",F101=""),"",IF(F101&lt;=0,"",IFERROR(J101/F101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>IF(OR(K101="",G101=""),"",IF(G101&lt;=0,"",IFERROR(K101/G101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L102" s="17">
+        <f>IF(OR(L101="",H101=""),"",IF(H101&lt;=0,"",IFERROR(L101/H101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M102" s="17">
+        <f>IF(OR(M101="",I101=""),"",IF(I101&lt;=0,"",IFERROR(M101/I101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N102" s="17">
+        <f>IF(OR(N101="",J101=""),"",IF(J101&lt;=0,"",IFERROR(N101/J101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V102" s="17">
+        <f>IF(OR(V101="",U101=""),"",IF(U101&lt;=0,"",IFERROR(V101/U101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W102" s="17">
+        <f>IF(OR(W101="",V101=""),"",IF(V101&lt;=0,"",IFERROR(W101/V101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X102" s="17">
+        <f>IF(OR(X101="",W101=""),"",IF(W101&lt;=0,"",IFERROR(X101/W101-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20" t="inlineStr">
+        <is>
+          <t>고정자산 매각이익</t>
+        </is>
+      </c>
+      <c r="E103" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H100" s="22" t="n">
-        <v>77.211</v>
-      </c>
-      <c r="I100" s="22" t="n">
-        <v>28.515</v>
-      </c>
-      <c r="L100" s="22" t="n">
+      <c r="H103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="22" t="n">
         <v>0.35</v>
       </c>
-      <c r="M100" s="22" t="n">
+      <c r="M103" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="22" t="n">
+      <c r="V103" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="W100" s="22" t="n">
-        <v>28.515</v>
-      </c>
-      <c r="X100" s="22" t="n">
+      <c r="W103" s="22" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="20" t="inlineStr">
-        <is>
-          <t>투자유가증권 매각손실</t>
-        </is>
-      </c>
-      <c r="H101" s="22" t="n">
+      <c r="X103" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="I101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>특별손실 합계</t>
-        </is>
-      </c>
-      <c r="H102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="W102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" s="22" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 중간순이익(손실)</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="n">
-        <v>-21.876</v>
-      </c>
-      <c r="D103" s="12" t="n">
-        <v>242.206</v>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v>2115.762</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>65.971</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>283.368</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>799.158</v>
-      </c>
-      <c r="I103" s="12" t="n">
-        <v>1740.077</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>-206.95</v>
-      </c>
-      <c r="K103" s="12" t="n">
-        <v>537.593</v>
-      </c>
-      <c r="L103" s="12" t="n">
-        <v>384.863</v>
-      </c>
-      <c r="M103" s="12" t="n">
-        <v>1392.237</v>
-      </c>
-      <c r="N103" s="12" t="n">
-        <v>28.064</v>
-      </c>
-      <c r="V103" s="12" t="n">
-        <v>2115.762</v>
-      </c>
-      <c r="W103" s="12" t="n">
-        <v>1740.077</v>
-      </c>
-      <c r="X103" s="12" t="n">
-        <v>1392.237</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
-        </is>
-      </c>
-      <c r="C104" s="22" t="n">
-        <v>20.277</v>
-      </c>
-      <c r="D104" s="22" t="n">
-        <v>35.279</v>
+          <t>투자유가증권 매각이익</t>
+        </is>
       </c>
       <c r="E104" s="22" t="n">
-        <v>541.1180000000001</v>
-      </c>
-      <c r="F104" s="22" t="n">
-        <v>49.728</v>
-      </c>
-      <c r="G104" s="22" t="n">
-        <v>48.771</v>
-      </c>
-      <c r="H104" s="22" t="n">
-        <v>187.492</v>
+        <v>0</v>
       </c>
       <c r="I104" s="22" t="n">
-        <v>504.324</v>
-      </c>
-      <c r="J104" s="22" t="n">
-        <v>3.532</v>
-      </c>
-      <c r="K104" s="22" t="n">
-        <v>51.422</v>
-      </c>
-      <c r="L104" s="22" t="n">
-        <v>29.504</v>
+        <v>28.515</v>
       </c>
       <c r="M104" s="22" t="n">
-        <v>446.691</v>
-      </c>
-      <c r="N104" s="22" t="n">
-        <v>56.472</v>
+        <v>0</v>
       </c>
       <c r="V104" s="22" t="n">
-        <v>541.1180000000001</v>
+        <v>0</v>
       </c>
       <c r="W104" s="22" t="n">
-        <v>504.324</v>
+        <v>28.515</v>
       </c>
       <c r="X104" s="22" t="n">
-        <v>446.691</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C105" s="22" t="n">
-        <v>-3.855</v>
-      </c>
-      <c r="D105" s="22" t="n">
-        <v>52.426</v>
+          <t>특별이익 합계</t>
+        </is>
       </c>
       <c r="E105" s="22" t="n">
-        <v>3.465</v>
-      </c>
-      <c r="F105" s="22" t="n">
-        <v>-23.047</v>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>48.886</v>
+        <v>0</v>
       </c>
       <c r="H105" s="22" t="n">
-        <v>68.52</v>
+        <v>77.211</v>
       </c>
       <c r="I105" s="22" t="n">
-        <v>-202.65</v>
-      </c>
-      <c r="J105" s="22" t="n">
-        <v>-71.56100000000001</v>
-      </c>
-      <c r="K105" s="22" t="n">
-        <v>126.218</v>
+        <v>28.515</v>
       </c>
       <c r="L105" s="22" t="n">
-        <v>93.70399999999999</v>
+        <v>0.35</v>
       </c>
       <c r="M105" s="22" t="n">
-        <v>-90.001</v>
-      </c>
-      <c r="N105" s="22" t="n">
-        <v>-34.845</v>
+        <v>0</v>
       </c>
       <c r="V105" s="22" t="n">
-        <v>3.465</v>
+        <v>0</v>
       </c>
       <c r="W105" s="22" t="n">
-        <v>-202.65</v>
+        <v>28.515</v>
       </c>
       <c r="X105" s="22" t="n">
-        <v>-90.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
-        </is>
-      </c>
-      <c r="C106" s="22" t="n">
-        <v>16.422</v>
-      </c>
-      <c r="D106" s="22" t="n">
-        <v>87.705</v>
-      </c>
-      <c r="E106" s="22" t="n">
-        <v>544.583</v>
-      </c>
-      <c r="F106" s="22" t="n">
-        <v>26.681</v>
-      </c>
-      <c r="G106" s="22" t="n">
-        <v>97.658</v>
+          <t>투자유가증권 매각손실</t>
+        </is>
       </c>
       <c r="H106" s="22" t="n">
-        <v>256.012</v>
+        <v>0</v>
       </c>
       <c r="I106" s="22" t="n">
-        <v>301.673</v>
-      </c>
-      <c r="J106" s="22" t="n">
-        <v>-68.02800000000001</v>
-      </c>
-      <c r="K106" s="22" t="n">
-        <v>177.639</v>
+        <v>0</v>
       </c>
       <c r="L106" s="22" t="n">
-        <v>123.208</v>
+        <v>0</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>356.691</v>
-      </c>
-      <c r="N106" s="22" t="n">
-        <v>21.627</v>
-      </c>
-      <c r="V106" s="22" t="n">
-        <v>544.583</v>
+        <v>0</v>
       </c>
       <c r="W106" s="22" t="n">
-        <v>301.673</v>
+        <v>0</v>
       </c>
       <c r="X106" s="22" t="n">
-        <v>356.691</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
-        <is>
-          <t>중간순이익(손실)</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="n">
-        <v>-38.298</v>
-      </c>
-      <c r="D107" s="12" t="n">
-        <v>154.5</v>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v>1571.179</v>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>39.29</v>
-      </c>
-      <c r="G107" s="12" t="n">
-        <v>185.709</v>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>543.147</v>
-      </c>
-      <c r="I107" s="12" t="n">
-        <v>1438.404</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>-138.921</v>
-      </c>
-      <c r="K107" s="12" t="n">
-        <v>359.952</v>
-      </c>
-      <c r="L107" s="12" t="n">
-        <v>261.656</v>
-      </c>
-      <c r="M107" s="12" t="n">
-        <v>1035.545</v>
-      </c>
-      <c r="N107" s="12" t="n">
-        <v>6.436</v>
-      </c>
-      <c r="V107" s="12" t="n">
-        <v>1571.179</v>
-      </c>
-      <c r="W107" s="12" t="n">
-        <v>1438.404</v>
-      </c>
-      <c r="X107" s="12" t="n">
-        <v>1035.545</v>
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="H107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
+          <t>법인세차감전 중간순이익(손실)</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>-21.876</v>
+      </c>
+      <c r="D108" s="12" t="n">
+        <v>242.206</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>2115.762</v>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>65.971</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>283.368</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>799.158</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>1740.077</v>
+      </c>
+      <c r="J108" s="12" t="n">
+        <v>-206.95</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>537.593</v>
+      </c>
+      <c r="L108" s="12" t="n">
+        <v>384.863</v>
+      </c>
+      <c r="M108" s="12" t="n">
+        <v>1392.237</v>
+      </c>
+      <c r="N108" s="12" t="n">
+        <v>28.064</v>
+      </c>
+      <c r="V108" s="12" t="n">
+        <v>2115.762</v>
+      </c>
+      <c r="W108" s="12" t="n">
+        <v>1740.077</v>
+      </c>
+      <c r="X108" s="12" t="n">
+        <v>1392.237</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="n">
+        <v>20.277</v>
+      </c>
+      <c r="D109" s="22" t="n">
+        <v>35.279</v>
+      </c>
+      <c r="E109" s="22" t="n">
+        <v>541.1180000000001</v>
+      </c>
+      <c r="F109" s="22" t="n">
+        <v>49.728</v>
+      </c>
+      <c r="G109" s="22" t="n">
+        <v>48.771</v>
+      </c>
+      <c r="H109" s="22" t="n">
+        <v>187.492</v>
+      </c>
+      <c r="I109" s="22" t="n">
+        <v>504.324</v>
+      </c>
+      <c r="J109" s="22" t="n">
+        <v>3.532</v>
+      </c>
+      <c r="K109" s="22" t="n">
+        <v>51.422</v>
+      </c>
+      <c r="L109" s="22" t="n">
+        <v>29.504</v>
+      </c>
+      <c r="M109" s="22" t="n">
+        <v>446.691</v>
+      </c>
+      <c r="N109" s="22" t="n">
+        <v>56.472</v>
+      </c>
+      <c r="V109" s="22" t="n">
+        <v>541.1180000000001</v>
+      </c>
+      <c r="W109" s="22" t="n">
+        <v>504.324</v>
+      </c>
+      <c r="X109" s="22" t="n">
+        <v>446.691</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C110" s="22" t="n">
+        <v>-3.855</v>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>52.426</v>
+      </c>
+      <c r="E110" s="22" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="F110" s="22" t="n">
+        <v>-23.047</v>
+      </c>
+      <c r="G110" s="22" t="n">
+        <v>48.886</v>
+      </c>
+      <c r="H110" s="22" t="n">
+        <v>68.52</v>
+      </c>
+      <c r="I110" s="22" t="n">
+        <v>-202.65</v>
+      </c>
+      <c r="J110" s="22" t="n">
+        <v>-71.56100000000001</v>
+      </c>
+      <c r="K110" s="22" t="n">
+        <v>126.218</v>
+      </c>
+      <c r="L110" s="22" t="n">
+        <v>93.70399999999999</v>
+      </c>
+      <c r="M110" s="22" t="n">
+        <v>-90.001</v>
+      </c>
+      <c r="N110" s="22" t="n">
+        <v>-34.845</v>
+      </c>
+      <c r="V110" s="22" t="n">
+        <v>3.465</v>
+      </c>
+      <c r="W110" s="22" t="n">
+        <v>-202.65</v>
+      </c>
+      <c r="X110" s="22" t="n">
+        <v>-90.001</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C111" s="22" t="n">
+        <v>16.422</v>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>87.705</v>
+      </c>
+      <c r="E111" s="22" t="n">
+        <v>544.583</v>
+      </c>
+      <c r="F111" s="22" t="n">
+        <v>26.681</v>
+      </c>
+      <c r="G111" s="22" t="n">
+        <v>97.658</v>
+      </c>
+      <c r="H111" s="22" t="n">
+        <v>256.012</v>
+      </c>
+      <c r="I111" s="22" t="n">
+        <v>301.673</v>
+      </c>
+      <c r="J111" s="22" t="n">
+        <v>-68.02800000000001</v>
+      </c>
+      <c r="K111" s="22" t="n">
+        <v>177.639</v>
+      </c>
+      <c r="L111" s="22" t="n">
+        <v>123.208</v>
+      </c>
+      <c r="M111" s="22" t="n">
+        <v>356.691</v>
+      </c>
+      <c r="N111" s="22" t="n">
+        <v>21.627</v>
+      </c>
+      <c r="V111" s="22" t="n">
+        <v>544.583</v>
+      </c>
+      <c r="W111" s="22" t="n">
+        <v>301.673</v>
+      </c>
+      <c r="X111" s="22" t="n">
+        <v>356.691</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>중간순이익(손실)</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="n">
+        <v>-38.298</v>
+      </c>
+      <c r="D112" s="12" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>1571.179</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>185.709</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>543.147</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>1438.404</v>
+      </c>
+      <c r="J112" s="12" t="n">
+        <v>-138.921</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>359.952</v>
+      </c>
+      <c r="L112" s="12" t="n">
+        <v>261.656</v>
+      </c>
+      <c r="M112" s="12" t="n">
+        <v>1035.545</v>
+      </c>
+      <c r="N112" s="12" t="n">
+        <v>6.436</v>
+      </c>
+      <c r="V112" s="12" t="n">
+        <v>1571.179</v>
+      </c>
+      <c r="W112" s="12" t="n">
+        <v>1438.404</v>
+      </c>
+      <c r="X112" s="12" t="n">
+        <v>1035.545</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G113" s="17">
+        <f>IF(OR(G112="",C112=""),"",IF(C112&lt;=0,"",IFERROR(G112/C112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H113" s="17">
+        <f>IF(OR(H112="",D112=""),"",IF(D112&lt;=0,"",IFERROR(H112/D112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I113" s="17">
+        <f>IF(OR(I112="",E112=""),"",IF(E112&lt;=0,"",IFERROR(I112/E112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J113" s="17">
+        <f>IF(OR(J112="",F112=""),"",IF(F112&lt;=0,"",IFERROR(J112/F112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>IF(OR(K112="",G112=""),"",IF(G112&lt;=0,"",IFERROR(K112/G112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L113" s="17">
+        <f>IF(OR(L112="",H112=""),"",IF(H112&lt;=0,"",IFERROR(L112/H112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M113" s="17">
+        <f>IF(OR(M112="",I112=""),"",IF(I112&lt;=0,"",IFERROR(M112/I112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N113" s="17">
+        <f>IF(OR(N112="",J112=""),"",IF(J112&lt;=0,"",IFERROR(N112/J112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V113" s="17">
+        <f>IF(OR(V112="",U112=""),"",IF(U112&lt;=0,"",IFERROR(V112/U112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W113" s="17">
+        <f>IF(OR(W112="",V112=""),"",IF(V112&lt;=0,"",IFERROR(W112/V112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X113" s="17">
+        <f>IF(OR(X112="",W112=""),"",IF(W112&lt;=0,"",IFERROR(X112/W112-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
           <t>비지배주주 순이익</t>
         </is>
       </c>
-      <c r="C108" s="12" t="n">
+      <c r="C114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="12" t="n">
+      <c r="D114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="12" t="n">
+      <c r="E114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="12" t="n">
+      <c r="F114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="12" t="n">
+      <c r="G114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H108" s="12" t="n">
+      <c r="H114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I108" s="12" t="n">
+      <c r="I114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J108" s="12" t="n">
+      <c r="J114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K108" s="12" t="n">
+      <c r="K114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L108" s="12" t="n">
+      <c r="L114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M108" s="12" t="n">
+      <c r="M114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N108" s="12" t="n">
+      <c r="N114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="12" t="n">
+      <c r="V114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="W108" s="12" t="n">
+      <c r="W114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="X108" s="12" t="n">
+      <c r="X114" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>지배주주 귀속 중간순이익(손실)</t>
         </is>
       </c>
-      <c r="C109" s="12" t="n">
+      <c r="C115" s="12" t="n">
         <v>-38.298</v>
       </c>
-      <c r="D109" s="12" t="n">
+      <c r="D115" s="12" t="n">
         <v>154.5</v>
       </c>
-      <c r="E109" s="12" t="n">
+      <c r="E115" s="12" t="n">
         <v>1571.179</v>
       </c>
-      <c r="F109" s="12" t="n">
+      <c r="F115" s="12" t="n">
         <v>39.29</v>
       </c>
-      <c r="G109" s="12" t="n">
+      <c r="G115" s="12" t="n">
         <v>185.709</v>
       </c>
-      <c r="H109" s="12" t="n">
+      <c r="H115" s="12" t="n">
         <v>543.147</v>
       </c>
-      <c r="I109" s="12" t="n">
+      <c r="I115" s="12" t="n">
         <v>1438.404</v>
       </c>
-      <c r="J109" s="12" t="n">
+      <c r="J115" s="12" t="n">
         <v>-138.921</v>
       </c>
-      <c r="K109" s="12" t="n">
+      <c r="K115" s="12" t="n">
         <v>359.952</v>
       </c>
-      <c r="L109" s="12" t="n">
+      <c r="L115" s="12" t="n">
         <v>261.656</v>
       </c>
-      <c r="M109" s="12" t="n">
+      <c r="M115" s="12" t="n">
         <v>1035.545</v>
       </c>
-      <c r="N109" s="12" t="n">
+      <c r="N115" s="12" t="n">
         <v>6.436</v>
       </c>
-      <c r="V109" s="12" t="n">
+      <c r="V115" s="12" t="n">
         <v>1571.179</v>
       </c>
-      <c r="W109" s="12" t="n">
+      <c r="W115" s="12" t="n">
         <v>1438.404</v>
       </c>
-      <c r="X109" s="12" t="n">
+      <c r="X115" s="12" t="n">
         <v>1035.545</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="18" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G116" s="17">
+        <f>IF(OR(G115="",C115=""),"",IF(C115&lt;=0,"",IFERROR(G115/C115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H116" s="17">
+        <f>IF(OR(H115="",D115=""),"",IF(D115&lt;=0,"",IFERROR(H115/D115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I116" s="17">
+        <f>IF(OR(I115="",E115=""),"",IF(E115&lt;=0,"",IFERROR(I115/E115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J116" s="17">
+        <f>IF(OR(J115="",F115=""),"",IF(F115&lt;=0,"",IFERROR(J115/F115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K116" s="17">
+        <f>IF(OR(K115="",G115=""),"",IF(G115&lt;=0,"",IFERROR(K115/G115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L116" s="17">
+        <f>IF(OR(L115="",H115=""),"",IF(H115&lt;=0,"",IFERROR(L115/H115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M116" s="17">
+        <f>IF(OR(M115="",I115=""),"",IF(I115&lt;=0,"",IFERROR(M115/I115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N116" s="17">
+        <f>IF(OR(N115="",J115=""),"",IF(J115&lt;=0,"",IFERROR(N115/J115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V116" s="17">
+        <f>IF(OR(V115="",U115=""),"",IF(U115&lt;=0,"",IFERROR(V115/U115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W116" s="17">
+        <f>IF(OR(W115="",V115=""),"",IF(V115&lt;=0,"",IFERROR(W115/V115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X116" s="17">
+        <f>IF(OR(X115="",W115=""),"",IF(W115&lt;=0,"",IFERROR(X115/W115-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
         <is>
           <t>포괄손익 · 전 항목</t>
         </is>
       </c>
-      <c r="B111" s="44" t="inlineStr">
+      <c r="B118" s="44" t="inlineStr">
         <is>
           <t>분기 = 3개월 단독</t>
         </is>
       </c>
-      <c r="C111" s="18" t="n"/>
-      <c r="D111" s="18" t="n"/>
-      <c r="E111" s="18" t="n"/>
-      <c r="F111" s="18" t="n"/>
-      <c r="G111" s="18" t="n"/>
-      <c r="H111" s="18" t="n"/>
-      <c r="I111" s="18" t="n"/>
-      <c r="J111" s="18" t="n"/>
-      <c r="K111" s="18" t="n"/>
-      <c r="L111" s="18" t="n"/>
-      <c r="M111" s="18" t="n"/>
-      <c r="N111" s="18" t="n"/>
-      <c r="O111" s="18" t="n"/>
-      <c r="P111" s="18" t="n"/>
-      <c r="Q111" s="18" t="n"/>
-      <c r="R111" s="18" t="n"/>
-      <c r="S111" s="18" t="n"/>
-      <c r="T111" s="18" t="n"/>
-      <c r="U111" s="18" t="n"/>
-      <c r="V111" s="18" t="n"/>
-      <c r="W111" s="18" t="n"/>
-      <c r="X111" s="18" t="n"/>
-      <c r="Y111" s="18" t="n"/>
-      <c r="Z111" s="18" t="n"/>
-      <c r="AA111" s="18" t="n"/>
-      <c r="AB111" s="18" t="n"/>
-      <c r="AC111" s="18" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="C118" s="18" t="n"/>
+      <c r="D118" s="18" t="n"/>
+      <c r="E118" s="18" t="n"/>
+      <c r="F118" s="18" t="n"/>
+      <c r="G118" s="18" t="n"/>
+      <c r="H118" s="18" t="n"/>
+      <c r="I118" s="18" t="n"/>
+      <c r="J118" s="18" t="n"/>
+      <c r="K118" s="18" t="n"/>
+      <c r="L118" s="18" t="n"/>
+      <c r="M118" s="18" t="n"/>
+      <c r="N118" s="18" t="n"/>
+      <c r="O118" s="18" t="n"/>
+      <c r="P118" s="18" t="n"/>
+      <c r="Q118" s="18" t="n"/>
+      <c r="R118" s="18" t="n"/>
+      <c r="S118" s="18" t="n"/>
+      <c r="T118" s="18" t="n"/>
+      <c r="U118" s="18" t="n"/>
+      <c r="V118" s="18" t="n"/>
+      <c r="W118" s="18" t="n"/>
+      <c r="X118" s="18" t="n"/>
+      <c r="Y118" s="18" t="n"/>
+      <c r="Z118" s="18" t="n"/>
+      <c r="AA118" s="18" t="n"/>
+      <c r="AB118" s="18" t="n"/>
+      <c r="AC118" s="18" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B112" s="5" t="inlineStr">
+      <c r="B119" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E112" s="5" t="inlineStr">
+      <c r="E119" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr">
+      <c r="F119" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G112" s="5" t="inlineStr">
+      <c r="G119" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H112" s="5" t="inlineStr">
+      <c r="H119" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I112" s="5" t="inlineStr">
+      <c r="I119" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J112" s="5" t="inlineStr">
+      <c r="J119" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K112" s="5" t="inlineStr">
+      <c r="K119" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L112" s="5" t="inlineStr">
+      <c r="L119" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M112" s="5" t="inlineStr">
+      <c r="M119" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N112" s="5" t="inlineStr">
+      <c r="N119" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O112" s="5" t="inlineStr">
+      <c r="O119" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P112" s="5" t="inlineStr">
+      <c r="P119" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q112" s="5" t="inlineStr">
+      <c r="Q119" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R112" s="5" t="inlineStr">
+      <c r="R119" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S112" s="5" t="inlineStr">
+      <c r="S119" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T112" s="5" t="inlineStr">
+      <c r="T119" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U112" s="5" t="inlineStr">
+      <c r="U119" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V112" s="5" t="inlineStr">
+      <c r="V119" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W112" s="5" t="inlineStr">
+      <c r="W119" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X112" s="5" t="inlineStr">
+      <c r="X119" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y112" s="5" t="inlineStr">
+      <c r="Y119" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z112" s="5" t="inlineStr">
+      <c r="Z119" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA112" s="5" t="inlineStr">
+      <c r="AA119" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB112" s="5" t="inlineStr">
+      <c r="AB119" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC112" s="5" t="inlineStr">
+      <c r="AC119" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="9" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>중간순이익(손실)</t>
         </is>
       </c>
-      <c r="C113" s="12" t="n">
+      <c r="C120" s="12" t="n">
         <v>-38.298</v>
       </c>
-      <c r="D113" s="12" t="n">
+      <c r="D120" s="12" t="n">
         <v>154.5</v>
       </c>
-      <c r="E113" s="12" t="n">
+      <c r="E120" s="12" t="n">
         <v>1571.179</v>
       </c>
-      <c r="F113" s="12" t="n">
+      <c r="F120" s="12" t="n">
         <v>39.29</v>
       </c>
-      <c r="G113" s="12" t="n">
+      <c r="G120" s="12" t="n">
         <v>185.709</v>
       </c>
-      <c r="H113" s="12" t="n">
+      <c r="H120" s="12" t="n">
         <v>543.147</v>
       </c>
-      <c r="I113" s="12" t="n">
+      <c r="I120" s="12" t="n">
         <v>1438.404</v>
       </c>
-      <c r="J113" s="12" t="n">
+      <c r="J120" s="12" t="n">
         <v>-138.921</v>
       </c>
-      <c r="K113" s="12" t="n">
+      <c r="K120" s="12" t="n">
         <v>359.952</v>
       </c>
-      <c r="L113" s="12" t="n">
+      <c r="L120" s="12" t="n">
         <v>261.656</v>
       </c>
-      <c r="M113" s="12" t="n">
+      <c r="M120" s="12" t="n">
         <v>1035.545</v>
       </c>
-      <c r="N113" s="12" t="n">
+      <c r="N120" s="12" t="n">
         <v>6.436</v>
       </c>
-      <c r="V113" s="12" t="n">
+      <c r="V120" s="12" t="n">
         <v>1571.179</v>
       </c>
-      <c r="W113" s="12" t="n">
+      <c r="W120" s="12" t="n">
         <v>1438.404</v>
       </c>
-      <c r="X113" s="12" t="n">
+      <c r="X120" s="12" t="n">
         <v>1035.545</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="20" t="inlineStr">
         <is>
           <t>기타유가증권 평가차액</t>
         </is>
       </c>
-      <c r="C114" s="22" t="n">
+      <c r="C121" s="22" t="n">
         <v>46.829</v>
       </c>
-      <c r="D114" s="22" t="n">
+      <c r="D121" s="22" t="n">
         <v>12.055</v>
       </c>
-      <c r="E114" s="22" t="n">
+      <c r="E121" s="22" t="n">
         <v>109.992</v>
       </c>
-      <c r="F114" s="22" t="n">
+      <c r="F121" s="22" t="n">
         <v>56.068</v>
       </c>
-      <c r="G114" s="22" t="n">
+      <c r="G121" s="22" t="n">
         <v>-100.182</v>
       </c>
-      <c r="H114" s="22" t="n">
+      <c r="H121" s="22" t="n">
         <v>-12.389</v>
       </c>
-      <c r="I114" s="22" t="n">
+      <c r="I121" s="22" t="n">
         <v>-19.832</v>
       </c>
-      <c r="J114" s="22" t="n">
+      <c r="J121" s="22" t="n">
         <v>39.547</v>
       </c>
-      <c r="K114" s="22" t="n">
+      <c r="K121" s="22" t="n">
         <v>108.549</v>
       </c>
-      <c r="L114" s="22" t="n">
+      <c r="L121" s="22" t="n">
         <v>65.111</v>
       </c>
-      <c r="M114" s="22" t="n">
+      <c r="M121" s="22" t="n">
         <v>39.139</v>
       </c>
-      <c r="N114" s="22" t="n">
+      <c r="N121" s="22" t="n">
         <v>111.699</v>
       </c>
-      <c r="V114" s="22" t="n">
+      <c r="V121" s="22" t="n">
         <v>109.992</v>
       </c>
-      <c r="W114" s="22" t="n">
+      <c r="W121" s="22" t="n">
         <v>-19.832</v>
       </c>
-      <c r="X114" s="22" t="n">
+      <c r="X121" s="22" t="n">
         <v>39.139</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
         <is>
           <t>퇴직급여 조정액</t>
         </is>
       </c>
-      <c r="C115" s="22" t="n">
+      <c r="C122" s="22" t="n">
         <v>-10.247</v>
       </c>
-      <c r="D115" s="22" t="n">
+      <c r="D122" s="22" t="n">
         <v>-10.247</v>
       </c>
-      <c r="E115" s="22" t="n">
+      <c r="E122" s="22" t="n">
         <v>303.63</v>
       </c>
-      <c r="F115" s="22" t="n">
+      <c r="F122" s="22" t="n">
         <v>-14.186</v>
       </c>
-      <c r="G115" s="22" t="n">
+      <c r="G122" s="22" t="n">
         <v>-14.186</v>
       </c>
-      <c r="H115" s="22" t="n">
+      <c r="H122" s="22" t="n">
         <v>-14.186</v>
       </c>
-      <c r="I115" s="22" t="n">
+      <c r="I122" s="22" t="n">
         <v>-57.225</v>
       </c>
-      <c r="J115" s="22" t="n">
+      <c r="J122" s="22" t="n">
         <v>-7.902</v>
       </c>
-      <c r="K115" s="22" t="n">
+      <c r="K122" s="22" t="n">
         <v>-7.902</v>
       </c>
-      <c r="L115" s="22" t="n">
+      <c r="L122" s="22" t="n">
         <v>-7.902</v>
       </c>
-      <c r="M115" s="22" t="n">
+      <c r="M122" s="22" t="n">
         <v>317.219</v>
       </c>
-      <c r="N115" s="22" t="n">
+      <c r="N122" s="22" t="n">
         <v>-18.961</v>
       </c>
-      <c r="V115" s="22" t="n">
+      <c r="V122" s="22" t="n">
         <v>303.63</v>
       </c>
-      <c r="W115" s="22" t="n">
+      <c r="W122" s="22" t="n">
         <v>-57.225</v>
       </c>
-      <c r="X115" s="22" t="n">
+      <c r="X122" s="22" t="n">
         <v>317.219</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="20" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="20" t="inlineStr">
         <is>
           <t>기타포괄손익 합계</t>
         </is>
       </c>
-      <c r="C116" s="22" t="n">
+      <c r="C123" s="22" t="n">
         <v>36.581</v>
       </c>
-      <c r="D116" s="22" t="n">
+      <c r="D123" s="22" t="n">
         <v>1.809</v>
       </c>
-      <c r="E116" s="22" t="n">
+      <c r="E123" s="22" t="n">
         <v>413.622</v>
       </c>
-      <c r="F116" s="22" t="n">
+      <c r="F123" s="22" t="n">
         <v>41.882</v>
       </c>
-      <c r="G116" s="22" t="n">
+      <c r="G123" s="22" t="n">
         <v>-114.368</v>
       </c>
-      <c r="H116" s="22" t="n">
+      <c r="H123" s="22" t="n">
         <v>-26.575</v>
       </c>
-      <c r="I116" s="22" t="n">
+      <c r="I123" s="22" t="n">
         <v>-77.057</v>
       </c>
-      <c r="J116" s="22" t="n">
+      <c r="J123" s="22" t="n">
         <v>31.645</v>
       </c>
-      <c r="K116" s="22" t="n">
+      <c r="K123" s="22" t="n">
         <v>100.646</v>
       </c>
-      <c r="L116" s="22" t="n">
+      <c r="L123" s="22" t="n">
         <v>57.209</v>
       </c>
-      <c r="M116" s="22" t="n">
+      <c r="M123" s="22" t="n">
         <v>356.359</v>
       </c>
-      <c r="N116" s="22" t="n">
+      <c r="N123" s="22" t="n">
         <v>92.738</v>
       </c>
-      <c r="V116" s="22" t="n">
+      <c r="V123" s="22" t="n">
         <v>413.622</v>
       </c>
-      <c r="W116" s="22" t="n">
+      <c r="W123" s="22" t="n">
         <v>-77.057</v>
       </c>
-      <c r="X116" s="22" t="n">
+      <c r="X123" s="22" t="n">
         <v>356.359</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>포괄이익</t>
         </is>
       </c>
-      <c r="C117" s="12" t="n">
+      <c r="C124" s="12" t="n">
         <v>-1.717</v>
       </c>
-      <c r="D117" s="12" t="n">
+      <c r="D124" s="12" t="n">
         <v>156.31</v>
       </c>
-      <c r="E117" s="12" t="n">
+      <c r="E124" s="12" t="n">
         <v>1984.801</v>
       </c>
-      <c r="F117" s="12" t="n">
+      <c r="F124" s="12" t="n">
         <v>81.172</v>
       </c>
-      <c r="G117" s="12" t="n">
+      <c r="G124" s="12" t="n">
         <v>71.34099999999999</v>
       </c>
-      <c r="H117" s="12" t="n">
+      <c r="H124" s="12" t="n">
         <v>516.571</v>
       </c>
-      <c r="I117" s="12" t="n">
+      <c r="I124" s="12" t="n">
         <v>1361.347</v>
       </c>
-      <c r="J117" s="12" t="n">
+      <c r="J124" s="12" t="n">
         <v>-107.276</v>
       </c>
-      <c r="K117" s="12" t="n">
+      <c r="K124" s="12" t="n">
         <v>460.599</v>
       </c>
-      <c r="L117" s="12" t="n">
+      <c r="L124" s="12" t="n">
         <v>318.864</v>
       </c>
-      <c r="M117" s="12" t="n">
+      <c r="M124" s="12" t="n">
         <v>1391.905</v>
       </c>
-      <c r="N117" s="12" t="n">
+      <c r="N124" s="12" t="n">
         <v>99.175</v>
       </c>
-      <c r="V117" s="12" t="n">
+      <c r="V124" s="12" t="n">
         <v>1984.801</v>
       </c>
-      <c r="W117" s="12" t="n">
+      <c r="W124" s="12" t="n">
         <v>1361.347</v>
       </c>
-      <c r="X117" s="12" t="n">
+      <c r="X124" s="12" t="n">
         <v>1391.905</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C118" s="12" t="n">
+      <c r="C125" s="12" t="n">
         <v>-1.717</v>
       </c>
-      <c r="D118" s="12" t="n">
+      <c r="D125" s="12" t="n">
         <v>156.31</v>
       </c>
-      <c r="E118" s="12" t="n">
+      <c r="E125" s="12" t="n">
         <v>1984.801</v>
       </c>
-      <c r="F118" s="12" t="n">
+      <c r="F125" s="12" t="n">
         <v>81.172</v>
       </c>
-      <c r="G118" s="12" t="n">
+      <c r="G125" s="12" t="n">
         <v>71.34099999999999</v>
       </c>
-      <c r="H118" s="12" t="n">
+      <c r="H125" s="12" t="n">
         <v>516.571</v>
       </c>
-      <c r="I118" s="12" t="n">
+      <c r="I125" s="12" t="n">
         <v>1361.347</v>
       </c>
-      <c r="J118" s="12" t="n">
+      <c r="J125" s="12" t="n">
         <v>-107.276</v>
       </c>
-      <c r="K118" s="12" t="n">
+      <c r="K125" s="12" t="n">
         <v>460.599</v>
       </c>
-      <c r="L118" s="12" t="n">
+      <c r="L125" s="12" t="n">
         <v>318.864</v>
       </c>
-      <c r="M118" s="12" t="n">
+      <c r="M125" s="12" t="n">
         <v>1391.905</v>
       </c>
-      <c r="N118" s="12" t="n">
+      <c r="N125" s="12" t="n">
         <v>99.175</v>
       </c>
-      <c r="V118" s="12" t="n">
+      <c r="V125" s="12" t="n">
         <v>1984.801</v>
       </c>
-      <c r="W118" s="12" t="n">
+      <c r="W125" s="12" t="n">
         <v>1361.347</v>
       </c>
-      <c r="X118" s="12" t="n">
+      <c r="X125" s="12" t="n">
         <v>1391.905</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C119" s="12" t="n">
+      <c r="C126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D119" s="12" t="n">
+      <c r="D126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E119" s="12" t="n">
+      <c r="E126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F119" s="12" t="n">
+      <c r="F126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G119" s="12" t="n">
+      <c r="G126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H119" s="12" t="n">
+      <c r="H126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I119" s="12" t="n">
+      <c r="I126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J119" s="12" t="n">
+      <c r="J126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K119" s="12" t="n">
+      <c r="K126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L119" s="12" t="n">
+      <c r="L126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M119" s="12" t="n">
+      <c r="M126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N119" s="12" t="n">
+      <c r="N126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="V119" s="12" t="n">
+      <c r="V126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="W119" s="12" t="n">
+      <c r="W126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="12" t="n">
+      <c r="X126" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="18" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B121" s="44" t="inlineStr">
+      <c r="B128" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C121" s="18" t="n"/>
-      <c r="D121" s="18" t="n"/>
-      <c r="E121" s="18" t="n"/>
-      <c r="F121" s="18" t="n"/>
-      <c r="G121" s="18" t="n"/>
-      <c r="H121" s="18" t="n"/>
-      <c r="I121" s="18" t="n"/>
-      <c r="J121" s="18" t="n"/>
-      <c r="K121" s="18" t="n"/>
-      <c r="L121" s="18" t="n"/>
-      <c r="M121" s="18" t="n"/>
-      <c r="N121" s="18" t="n"/>
-      <c r="O121" s="18" t="n"/>
-      <c r="P121" s="18" t="n"/>
-      <c r="Q121" s="18" t="n"/>
-      <c r="R121" s="18" t="n"/>
-      <c r="S121" s="18" t="n"/>
-      <c r="T121" s="18" t="n"/>
-      <c r="U121" s="18" t="n"/>
-      <c r="V121" s="18" t="n"/>
-      <c r="W121" s="18" t="n"/>
-      <c r="X121" s="18" t="n"/>
-      <c r="Y121" s="18" t="n"/>
-      <c r="Z121" s="18" t="n"/>
-      <c r="AA121" s="18" t="n"/>
-      <c r="AB121" s="18" t="n"/>
-      <c r="AC121" s="18" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
+      <c r="C128" s="18" t="n"/>
+      <c r="D128" s="18" t="n"/>
+      <c r="E128" s="18" t="n"/>
+      <c r="F128" s="18" t="n"/>
+      <c r="G128" s="18" t="n"/>
+      <c r="H128" s="18" t="n"/>
+      <c r="I128" s="18" t="n"/>
+      <c r="J128" s="18" t="n"/>
+      <c r="K128" s="18" t="n"/>
+      <c r="L128" s="18" t="n"/>
+      <c r="M128" s="18" t="n"/>
+      <c r="N128" s="18" t="n"/>
+      <c r="O128" s="18" t="n"/>
+      <c r="P128" s="18" t="n"/>
+      <c r="Q128" s="18" t="n"/>
+      <c r="R128" s="18" t="n"/>
+      <c r="S128" s="18" t="n"/>
+      <c r="T128" s="18" t="n"/>
+      <c r="U128" s="18" t="n"/>
+      <c r="V128" s="18" t="n"/>
+      <c r="W128" s="18" t="n"/>
+      <c r="X128" s="18" t="n"/>
+      <c r="Y128" s="18" t="n"/>
+      <c r="Z128" s="18" t="n"/>
+      <c r="AA128" s="18" t="n"/>
+      <c r="AB128" s="18" t="n"/>
+      <c r="AC128" s="18" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B122" s="5" t="inlineStr">
+      <c r="B129" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
+      <c r="C129" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E122" s="5" t="inlineStr">
+      <c r="E129" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr">
+      <c r="F129" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G122" s="5" t="inlineStr">
+      <c r="G129" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H122" s="5" t="inlineStr">
+      <c r="H129" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I122" s="5" t="inlineStr">
+      <c r="I129" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J122" s="5" t="inlineStr">
+      <c r="J129" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K122" s="5" t="inlineStr">
+      <c r="K129" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L122" s="5" t="inlineStr">
+      <c r="L129" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M122" s="5" t="inlineStr">
+      <c r="M129" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N122" s="5" t="inlineStr">
+      <c r="N129" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O122" s="5" t="inlineStr">
+      <c r="O129" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P122" s="5" t="inlineStr">
+      <c r="P129" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q122" s="5" t="inlineStr">
+      <c r="Q129" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R122" s="5" t="inlineStr">
+      <c r="R129" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S122" s="5" t="inlineStr">
+      <c r="S129" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T122" s="5" t="inlineStr">
+      <c r="T129" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U122" s="5" t="inlineStr">
+      <c r="U129" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V122" s="5" t="inlineStr">
+      <c r="V129" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W122" s="5" t="inlineStr">
+      <c r="W129" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X122" s="5" t="inlineStr">
+      <c r="X129" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y122" s="5" t="inlineStr">
+      <c r="Y129" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z122" s="5" t="inlineStr">
+      <c r="Z129" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA122" s="5" t="inlineStr">
+      <c r="AA129" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB122" s="5" t="inlineStr">
+      <c r="AB129" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC122" s="5" t="inlineStr">
+      <c r="AC129" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="C123" s="12" t="n">
+      <c r="C130" s="12" t="n">
         <v>-6.307</v>
       </c>
-      <c r="E123" s="12" t="n">
+      <c r="E130" s="12" t="n">
         <v>2351.661</v>
       </c>
-      <c r="G123" s="12" t="n">
+      <c r="G130" s="12" t="n">
         <v>349.339</v>
       </c>
-      <c r="I123" s="12" t="n">
+      <c r="I130" s="12" t="n">
         <v>2888.574</v>
       </c>
-      <c r="K123" s="12" t="n">
+      <c r="K130" s="12" t="n">
         <v>330.643</v>
       </c>
-      <c r="M123" s="12" t="n">
+      <c r="M130" s="12" t="n">
         <v>2107.743</v>
       </c>
-      <c r="U123" s="12" t="n">
+      <c r="U130" s="12" t="n">
         <v>2211.919</v>
       </c>
-      <c r="V123" s="12" t="n">
+      <c r="V130" s="12" t="n">
         <v>2351.661</v>
       </c>
-      <c r="W123" s="12" t="n">
+      <c r="W130" s="12" t="n">
         <v>2888.574</v>
       </c>
-      <c r="X123" s="12" t="n">
+      <c r="X130" s="12" t="n">
         <v>2107.743</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="C124" s="22" t="n">
-        <v>185.204</v>
-      </c>
-      <c r="E124" s="22" t="n">
-        <v>372.714</v>
-      </c>
-      <c r="G124" s="22" t="n">
-        <v>175.168</v>
-      </c>
-      <c r="I124" s="22" t="n">
-        <v>372.425</v>
-      </c>
-      <c r="K124" s="22" t="n">
-        <v>184.374</v>
-      </c>
-      <c r="M124" s="22" t="n">
-        <v>381.502</v>
-      </c>
-      <c r="U124" s="22" t="n">
-        <v>326.133</v>
-      </c>
-      <c r="V124" s="22" t="n">
-        <v>372.714</v>
-      </c>
-      <c r="W124" s="22" t="n">
-        <v>372.425</v>
-      </c>
-      <c r="X124" s="22" t="n">
-        <v>381.502</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="C125" s="22" t="n">
-        <v>12.844</v>
-      </c>
-      <c r="E125" s="22" t="n">
-        <v>19.267</v>
-      </c>
-      <c r="G125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" s="22" t="n">
-        <v>25.689</v>
-      </c>
-      <c r="V125" s="22" t="n">
-        <v>19.267</v>
-      </c>
-      <c r="W125" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="C126" s="22" t="n">
-        <v>-0.423</v>
-      </c>
-      <c r="E126" s="22" t="n">
-        <v>6.698</v>
-      </c>
-      <c r="G126" s="22" t="n">
-        <v>-7.002</v>
-      </c>
-      <c r="I126" s="22" t="n">
-        <v>-6.649</v>
-      </c>
-      <c r="K126" s="22" t="n">
-        <v>-0.342</v>
-      </c>
-      <c r="M126" s="22" t="n">
-        <v>69.428</v>
-      </c>
-      <c r="U126" s="22" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="V126" s="22" t="n">
-        <v>6.698</v>
-      </c>
-      <c r="W126" s="22" t="n">
-        <v>-6.649</v>
-      </c>
-      <c r="X126" s="22" t="n">
-        <v>69.428</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C127" s="22" t="n">
-        <v>-0.168</v>
-      </c>
-      <c r="E127" s="22" t="n">
-        <v>-35.673</v>
-      </c>
-      <c r="G127" s="22" t="n">
-        <v>38.465</v>
-      </c>
-      <c r="I127" s="22" t="n">
-        <v>83.639</v>
-      </c>
-      <c r="K127" s="22" t="n">
-        <v>-50.188</v>
-      </c>
-      <c r="M127" s="22" t="n">
-        <v>-73.75700000000001</v>
-      </c>
-      <c r="U127" s="22" t="n">
-        <v>-79.036</v>
-      </c>
-      <c r="V127" s="22" t="n">
-        <v>-35.673</v>
-      </c>
-      <c r="W127" s="22" t="n">
-        <v>83.639</v>
-      </c>
-      <c r="X127" s="22" t="n">
-        <v>-73.75700000000001</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="20" t="inlineStr">
-        <is>
-          <t>임원 상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C128" s="22" t="n">
-        <v>-26.967</v>
-      </c>
-      <c r="E128" s="22" t="n">
-        <v>-6.513</v>
-      </c>
-      <c r="G128" s="22" t="n">
-        <v>-24.408</v>
-      </c>
-      <c r="I128" s="22" t="n">
-        <v>5.086</v>
-      </c>
-      <c r="K128" s="22" t="n">
-        <v>-23.026</v>
-      </c>
-      <c r="M128" s="22" t="n">
-        <v>4.782</v>
-      </c>
-      <c r="U128" s="22" t="n">
-        <v>7.171</v>
-      </c>
-      <c r="V128" s="22" t="n">
-        <v>-6.513</v>
-      </c>
-      <c r="W128" s="22" t="n">
-        <v>5.086</v>
-      </c>
-      <c r="X128" s="22" t="n">
-        <v>4.782</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>제품보증 충당금 증감</t>
-        </is>
-      </c>
-      <c r="C129" s="22" t="n">
-        <v>-4.265</v>
-      </c>
-      <c r="E129" s="22" t="n">
-        <v>-38.442</v>
-      </c>
-      <c r="G129" s="22" t="n">
-        <v>-0.641</v>
-      </c>
-      <c r="I129" s="22" t="n">
-        <v>27.238</v>
-      </c>
-      <c r="K129" s="22" t="n">
-        <v>-8.384</v>
-      </c>
-      <c r="M129" s="22" t="n">
-        <v>-15.669</v>
-      </c>
-      <c r="U129" s="22" t="n">
-        <v>26.743</v>
-      </c>
-      <c r="V129" s="22" t="n">
-        <v>-38.442</v>
-      </c>
-      <c r="W129" s="22" t="n">
-        <v>27.238</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>-15.669</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="20" t="inlineStr">
-        <is>
-          <t>Increase Decrease In Provision For Loss On Construction Contracts Ope CF</t>
-        </is>
-      </c>
-      <c r="C130" s="22" t="n">
-        <v>1.715</v>
-      </c>
-      <c r="E130" s="22" t="n">
-        <v>-16.3</v>
-      </c>
-      <c r="G130" s="22" t="n">
-        <v>14.224</v>
-      </c>
-      <c r="I130" s="22" t="n">
-        <v>4.892</v>
-      </c>
-      <c r="K130" s="22" t="n">
-        <v>-0.327</v>
-      </c>
-      <c r="M130" s="22" t="n">
-        <v>45.595</v>
-      </c>
-      <c r="U130" s="22" t="n">
-        <v>-31.897</v>
-      </c>
-      <c r="V130" s="22" t="n">
-        <v>-16.3</v>
-      </c>
-      <c r="W130" s="22" t="n">
-        <v>4.892</v>
-      </c>
-      <c r="X130" s="22" t="n">
-        <v>45.595</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>주식급여 충당금 증감</t>
-        </is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="C131" s="22" t="n">
+        <v>185.204</v>
+      </c>
+      <c r="E131" s="22" t="n">
+        <v>372.714</v>
+      </c>
+      <c r="G131" s="22" t="n">
+        <v>175.168</v>
       </c>
       <c r="I131" s="22" t="n">
-        <v>0</v>
+        <v>372.425</v>
+      </c>
+      <c r="K131" s="22" t="n">
+        <v>184.374</v>
       </c>
       <c r="M131" s="22" t="n">
-        <v>39.933</v>
+        <v>381.502</v>
+      </c>
+      <c r="U131" s="22" t="n">
+        <v>326.133</v>
+      </c>
+      <c r="V131" s="22" t="n">
+        <v>372.714</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>0</v>
+        <v>372.425</v>
       </c>
       <c r="X131" s="22" t="n">
-        <v>39.933</v>
+        <v>381.502</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
+          <t>영업권 상각</t>
         </is>
       </c>
       <c r="C132" s="22" t="n">
-        <v>-11.816</v>
+        <v>12.844</v>
       </c>
       <c r="E132" s="22" t="n">
-        <v>-25.472</v>
+        <v>19.267</v>
       </c>
       <c r="G132" s="22" t="n">
-        <v>-13.515</v>
+        <v>0</v>
       </c>
       <c r="I132" s="22" t="n">
-        <v>-31.282</v>
-      </c>
-      <c r="K132" s="22" t="n">
-        <v>-18.053</v>
-      </c>
-      <c r="M132" s="22" t="n">
-        <v>-43.128</v>
+        <v>0</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>-22.098</v>
+        <v>25.689</v>
       </c>
       <c r="V132" s="22" t="n">
-        <v>-25.472</v>
+        <v>19.267</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>-31.282</v>
-      </c>
-      <c r="X132" s="22" t="n">
-        <v>-43.128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
-        </is>
+          <t>대손충당금 증감</t>
+        </is>
+      </c>
+      <c r="C133" s="22" t="n">
+        <v>-0.423</v>
       </c>
       <c r="E133" s="22" t="n">
-        <v>0.029</v>
+        <v>6.698</v>
       </c>
       <c r="G133" s="22" t="n">
-        <v>0</v>
+        <v>-7.002</v>
       </c>
       <c r="I133" s="22" t="n">
-        <v>-105.726</v>
+        <v>-6.649</v>
       </c>
       <c r="K133" s="22" t="n">
-        <v>1.125</v>
+        <v>-0.342</v>
       </c>
       <c r="M133" s="22" t="n">
-        <v>1.125</v>
+        <v>69.428</v>
       </c>
       <c r="U133" s="22" t="n">
-        <v>-0.2</v>
+        <v>0.347</v>
       </c>
       <c r="V133" s="22" t="n">
-        <v>0.029</v>
+        <v>6.698</v>
       </c>
       <c r="W133" s="22" t="n">
-        <v>-105.726</v>
+        <v>-6.649</v>
       </c>
       <c r="X133" s="22" t="n">
-        <v>1.125</v>
+        <v>69.428</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각손익</t>
-        </is>
+          <t>상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="C134" s="22" t="n">
+        <v>-0.168</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>-0.209</v>
+        <v>-35.673</v>
       </c>
       <c r="G134" s="22" t="n">
-        <v>0</v>
+        <v>38.465</v>
       </c>
       <c r="I134" s="22" t="n">
-        <v>0</v>
+        <v>83.639</v>
       </c>
       <c r="K134" s="22" t="n">
-        <v>-314.526</v>
+        <v>-50.188</v>
       </c>
       <c r="M134" s="22" t="n">
-        <v>-314.876</v>
+        <v>-73.75700000000001</v>
       </c>
       <c r="U134" s="22" t="n">
-        <v>-45.94</v>
+        <v>-79.036</v>
       </c>
       <c r="V134" s="22" t="n">
-        <v>-0.209</v>
+        <v>-35.673</v>
       </c>
       <c r="W134" s="22" t="n">
-        <v>0</v>
+        <v>83.639</v>
       </c>
       <c r="X134" s="22" t="n">
-        <v>-314.876</v>
+        <v>-73.75700000000001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
+          <t>임원 상여충당금 증감</t>
         </is>
       </c>
       <c r="C135" s="22" t="n">
-        <v>0</v>
+        <v>-26.967</v>
       </c>
       <c r="E135" s="22" t="n">
-        <v>8.4</v>
+        <v>-6.513</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>6.011</v>
+        <v>-24.408</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>16.494</v>
+        <v>5.086</v>
       </c>
       <c r="K135" s="22" t="n">
-        <v>-3.758</v>
+        <v>-23.026</v>
       </c>
       <c r="M135" s="22" t="n">
-        <v>5.133</v>
+        <v>4.782</v>
       </c>
       <c r="U135" s="22" t="n">
-        <v>24.434</v>
+        <v>7.171</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>8.4</v>
+        <v>-6.513</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>16.494</v>
+        <v>5.086</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>5.133</v>
+        <v>4.782</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>사업양도 손익</t>
-        </is>
+          <t>제품보증 충당금 증감</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="n">
+        <v>-4.265</v>
       </c>
       <c r="E136" s="22" t="n">
-        <v>0</v>
+        <v>-38.442</v>
+      </c>
+      <c r="G136" s="22" t="n">
+        <v>-0.641</v>
+      </c>
+      <c r="I136" s="22" t="n">
+        <v>27.238</v>
+      </c>
+      <c r="K136" s="22" t="n">
+        <v>-8.384</v>
+      </c>
+      <c r="M136" s="22" t="n">
+        <v>-15.669</v>
       </c>
       <c r="U136" s="22" t="n">
-        <v>273.206</v>
+        <v>26.743</v>
       </c>
       <c r="V136" s="22" t="n">
-        <v>0</v>
+        <v>-38.442</v>
+      </c>
+      <c r="W136" s="22" t="n">
+        <v>27.238</v>
+      </c>
+      <c r="X136" s="22" t="n">
+        <v>-15.669</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>Increase Decrease In Provision For Loss On Construction Contracts Ope CF</t>
         </is>
       </c>
       <c r="C137" s="22" t="n">
-        <v>4772.956</v>
+        <v>1.715</v>
       </c>
       <c r="E137" s="22" t="n">
-        <v>-566.968</v>
+        <v>-16.3</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>2262.346</v>
+        <v>14.224</v>
       </c>
       <c r="I137" s="22" t="n">
-        <v>-871.356</v>
+        <v>4.892</v>
       </c>
       <c r="K137" s="22" t="n">
-        <v>3651.894</v>
+        <v>-0.327</v>
       </c>
       <c r="M137" s="22" t="n">
-        <v>2507.036</v>
+        <v>45.595</v>
       </c>
       <c r="U137" s="22" t="n">
-        <v>-961.465</v>
+        <v>-31.897</v>
       </c>
       <c r="V137" s="22" t="n">
-        <v>-566.968</v>
+        <v>-16.3</v>
       </c>
       <c r="W137" s="22" t="n">
-        <v>-871.356</v>
+        <v>4.892</v>
       </c>
       <c r="X137" s="22" t="n">
-        <v>2507.036</v>
+        <v>45.595</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="C138" s="22" t="n">
-        <v>-485.45</v>
-      </c>
-      <c r="E138" s="22" t="n">
-        <v>136.332</v>
-      </c>
-      <c r="G138" s="22" t="n">
-        <v>-1306.428</v>
+          <t>주식급여 충당금 증감</t>
+        </is>
       </c>
       <c r="I138" s="22" t="n">
-        <v>77.098</v>
-      </c>
-      <c r="K138" s="22" t="n">
-        <v>-1095.507</v>
+        <v>0</v>
       </c>
       <c r="M138" s="22" t="n">
-        <v>796.4349999999999</v>
-      </c>
-      <c r="U138" s="22" t="n">
-        <v>24.096</v>
-      </c>
-      <c r="V138" s="22" t="n">
-        <v>136.332</v>
+        <v>39.933</v>
       </c>
       <c r="W138" s="22" t="n">
-        <v>77.098</v>
+        <v>0</v>
       </c>
       <c r="X138" s="22" t="n">
-        <v>796.4349999999999</v>
+        <v>39.933</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="C139" s="22" t="n">
-        <v>-1111.96</v>
+        <v>-11.816</v>
       </c>
       <c r="E139" s="22" t="n">
-        <v>-70.61</v>
+        <v>-25.472</v>
       </c>
       <c r="G139" s="22" t="n">
-        <v>-1566.271</v>
+        <v>-13.515</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>-1633.575</v>
+        <v>-31.282</v>
       </c>
       <c r="K139" s="22" t="n">
-        <v>-770.7430000000001</v>
+        <v>-18.053</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>-1019.221</v>
+        <v>-43.128</v>
       </c>
       <c r="U139" s="22" t="n">
-        <v>-456.919</v>
+        <v>-22.098</v>
       </c>
       <c r="V139" s="22" t="n">
-        <v>-70.61</v>
+        <v>-25.472</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>-1633.575</v>
+        <v>-31.282</v>
       </c>
       <c r="X139" s="22" t="n">
-        <v>-1019.221</v>
+        <v>-43.128</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
-        </is>
-      </c>
-      <c r="C140" s="22" t="n">
-        <v>-189.615</v>
+          <t>투자유가증권 매각손익</t>
+        </is>
       </c>
       <c r="E140" s="22" t="n">
-        <v>-142.375</v>
+        <v>0.029</v>
       </c>
       <c r="G140" s="22" t="n">
-        <v>9.497999999999999</v>
+        <v>0</v>
       </c>
       <c r="I140" s="22" t="n">
-        <v>226.959</v>
+        <v>-105.726</v>
       </c>
       <c r="K140" s="22" t="n">
-        <v>-181.057</v>
+        <v>1.125</v>
       </c>
       <c r="M140" s="22" t="n">
-        <v>464.953</v>
+        <v>1.125</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>122.911</v>
+        <v>-0.2</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>-142.375</v>
+        <v>0.029</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>226.959</v>
+        <v>-105.726</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>464.953</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C141" s="22" t="n">
-        <v>-322.208</v>
+          <t>유형자산 매각손익</t>
+        </is>
       </c>
       <c r="E141" s="22" t="n">
-        <v>-209.358</v>
+        <v>-0.209</v>
       </c>
       <c r="G141" s="22" t="n">
-        <v>-46.889</v>
+        <v>0</v>
       </c>
       <c r="I141" s="22" t="n">
-        <v>67.895</v>
+        <v>0</v>
       </c>
       <c r="K141" s="22" t="n">
-        <v>-126.254</v>
+        <v>-314.526</v>
       </c>
       <c r="M141" s="22" t="n">
-        <v>-65.133</v>
+        <v>-314.876</v>
       </c>
       <c r="U141" s="22" t="n">
-        <v>-185.205</v>
+        <v>-45.94</v>
       </c>
       <c r="V141" s="22" t="n">
-        <v>-209.358</v>
+        <v>-0.209</v>
       </c>
       <c r="W141" s="22" t="n">
-        <v>67.895</v>
+        <v>0</v>
       </c>
       <c r="X141" s="22" t="n">
-        <v>-65.133</v>
+        <v>-314.876</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>고정자산 제각손실</t>
         </is>
       </c>
       <c r="C142" s="22" t="n">
-        <v>2813.538</v>
+        <v>0</v>
       </c>
       <c r="E142" s="22" t="n">
-        <v>1783.178</v>
+        <v>8.4</v>
       </c>
       <c r="G142" s="22" t="n">
-        <v>-110.101</v>
+        <v>6.011</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>1121.714</v>
+        <v>16.494</v>
       </c>
       <c r="K142" s="22" t="n">
-        <v>1575.867</v>
+        <v>-3.758</v>
       </c>
       <c r="M142" s="22" t="n">
-        <v>4891.882</v>
+        <v>5.133</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>1259.89</v>
+        <v>24.434</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>1783.178</v>
+        <v>8.4</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>1121.714</v>
+        <v>16.494</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>4891.882</v>
+        <v>5.133</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
-        </is>
-      </c>
-      <c r="C143" s="22" t="n">
-        <v>11.816</v>
+          <t>사업양도 손익</t>
+        </is>
       </c>
       <c r="E143" s="22" t="n">
-        <v>25.472</v>
-      </c>
-      <c r="G143" s="22" t="n">
-        <v>13.515</v>
-      </c>
-      <c r="I143" s="22" t="n">
-        <v>31.282</v>
-      </c>
-      <c r="K143" s="22" t="n">
-        <v>18.053</v>
-      </c>
-      <c r="M143" s="22" t="n">
-        <v>43.128</v>
+        <v>0</v>
       </c>
       <c r="U143" s="22" t="n">
-        <v>22.098</v>
+        <v>273.206</v>
       </c>
       <c r="V143" s="22" t="n">
-        <v>25.472</v>
-      </c>
-      <c r="W143" s="22" t="n">
-        <v>31.282</v>
-      </c>
-      <c r="X143" s="22" t="n">
-        <v>43.128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>보험금 수취</t>
-        </is>
+          <t>매출채권 증감</t>
+        </is>
+      </c>
+      <c r="C144" s="22" t="n">
+        <v>4772.956</v>
       </c>
       <c r="E144" s="22" t="n">
-        <v>0.589</v>
+        <v>-566.968</v>
+      </c>
+      <c r="G144" s="22" t="n">
+        <v>2262.346</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>0.355</v>
+        <v>-871.356</v>
+      </c>
+      <c r="K144" s="22" t="n">
+        <v>3651.894</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>0.461</v>
+        <v>2507.036</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>0.591</v>
+        <v>-961.465</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>0.589</v>
+        <v>-566.968</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>0.355</v>
+        <v>-871.356</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>0.461</v>
+        <v>2507.036</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="C145" s="22" t="n">
-        <v>-343.074</v>
+        <v>-485.45</v>
       </c>
       <c r="E145" s="22" t="n">
-        <v>-398.944</v>
+        <v>136.332</v>
       </c>
       <c r="G145" s="22" t="n">
-        <v>-601.643</v>
+        <v>-1306.428</v>
       </c>
       <c r="I145" s="22" t="n">
-        <v>-719.941</v>
+        <v>77.098</v>
       </c>
       <c r="K145" s="22" t="n">
-        <v>-663.987</v>
+        <v>-1095.507</v>
       </c>
       <c r="M145" s="22" t="n">
-        <v>-1104.149</v>
+        <v>796.4349999999999</v>
       </c>
       <c r="U145" s="22" t="n">
-        <v>-665.624</v>
+        <v>24.096</v>
       </c>
       <c r="V145" s="22" t="n">
-        <v>-398.944</v>
+        <v>136.332</v>
       </c>
       <c r="W145" s="22" t="n">
-        <v>-719.941</v>
+        <v>77.098</v>
       </c>
       <c r="X145" s="22" t="n">
-        <v>-1104.149</v>
+        <v>796.4349999999999</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
-        </is>
+          <t>매입채무 증감</t>
+        </is>
+      </c>
+      <c r="C146" s="22" t="n">
+        <v>-1111.96</v>
+      </c>
+      <c r="E146" s="22" t="n">
+        <v>-70.61</v>
       </c>
       <c r="G146" s="22" t="n">
-        <v>0</v>
+        <v>-1566.271</v>
       </c>
       <c r="I146" s="22" t="n">
-        <v>0</v>
+        <v>-1633.575</v>
       </c>
       <c r="K146" s="22" t="n">
-        <v>40.716</v>
+        <v>-770.7430000000001</v>
       </c>
       <c r="M146" s="22" t="n">
-        <v>40.716</v>
+        <v>-1019.221</v>
+      </c>
+      <c r="U146" s="22" t="n">
+        <v>-456.919</v>
+      </c>
+      <c r="V146" s="22" t="n">
+        <v>-70.61</v>
       </c>
       <c r="W146" s="22" t="n">
-        <v>0</v>
+        <v>-1633.575</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>40.716</v>
+        <v>-1019.221</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C147" s="12" t="n">
-        <v>2482.281</v>
-      </c>
-      <c r="E147" s="12" t="n">
-        <v>1410.295</v>
-      </c>
-      <c r="G147" s="12" t="n">
-        <v>-698.229</v>
-      </c>
-      <c r="I147" s="12" t="n">
-        <v>433.41</v>
-      </c>
-      <c r="K147" s="12" t="n">
-        <v>970.65</v>
-      </c>
-      <c r="M147" s="12" t="n">
-        <v>3872.038</v>
-      </c>
-      <c r="U147" s="12" t="n">
-        <v>616.956</v>
-      </c>
-      <c r="V147" s="12" t="n">
-        <v>1410.295</v>
-      </c>
-      <c r="W147" s="12" t="n">
-        <v>433.41</v>
-      </c>
-      <c r="X147" s="12" t="n">
-        <v>3872.038</v>
+      <c r="A147" s="20" t="inlineStr">
+        <is>
+          <t>미지급 소비세 증감</t>
+        </is>
+      </c>
+      <c r="C147" s="22" t="n">
+        <v>-189.615</v>
+      </c>
+      <c r="E147" s="22" t="n">
+        <v>-142.375</v>
+      </c>
+      <c r="G147" s="22" t="n">
+        <v>9.497999999999999</v>
+      </c>
+      <c r="I147" s="22" t="n">
+        <v>226.959</v>
+      </c>
+      <c r="K147" s="22" t="n">
+        <v>-181.057</v>
+      </c>
+      <c r="M147" s="22" t="n">
+        <v>464.953</v>
+      </c>
+      <c r="U147" s="22" t="n">
+        <v>122.911</v>
+      </c>
+      <c r="V147" s="22" t="n">
+        <v>-142.375</v>
+      </c>
+      <c r="W147" s="22" t="n">
+        <v>226.959</v>
+      </c>
+      <c r="X147" s="22" t="n">
+        <v>464.953</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C148" s="22" t="n">
-        <v>-60.162</v>
+        <v>-322.208</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-176.198</v>
+        <v>-209.358</v>
       </c>
       <c r="G148" s="22" t="n">
-        <v>-149.6</v>
+        <v>-46.889</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>-402.524</v>
+        <v>67.895</v>
       </c>
       <c r="K148" s="22" t="n">
-        <v>-136.941</v>
+        <v>-126.254</v>
       </c>
       <c r="M148" s="22" t="n">
-        <v>-270.762</v>
+        <v>-65.133</v>
       </c>
       <c r="U148" s="22" t="n">
-        <v>-3750.162</v>
+        <v>-185.205</v>
       </c>
       <c r="V148" s="22" t="n">
-        <v>-176.198</v>
+        <v>-209.358</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>-402.524</v>
+        <v>67.895</v>
       </c>
       <c r="X148" s="22" t="n">
-        <v>-270.762</v>
+        <v>-65.133</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="C149" s="22" t="n">
+        <v>2813.538</v>
       </c>
       <c r="E149" s="22" t="n">
-        <v>0.209</v>
+        <v>1783.178</v>
       </c>
       <c r="G149" s="22" t="n">
-        <v>0</v>
+        <v>-110.101</v>
       </c>
       <c r="I149" s="22" t="n">
-        <v>0</v>
+        <v>1121.714</v>
       </c>
       <c r="K149" s="22" t="n">
-        <v>366.389</v>
+        <v>1575.867</v>
       </c>
       <c r="M149" s="22" t="n">
-        <v>370.457</v>
+        <v>4891.882</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>213.545</v>
+        <v>1259.89</v>
       </c>
       <c r="V149" s="22" t="n">
-        <v>0.209</v>
+        <v>1783.178</v>
       </c>
       <c r="W149" s="22" t="n">
-        <v>0</v>
+        <v>1121.714</v>
       </c>
       <c r="X149" s="22" t="n">
-        <v>370.457</v>
+        <v>4891.882</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="C150" s="22" t="n">
-        <v>-15.526</v>
+        <v>11.816</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>-35.692</v>
+        <v>25.472</v>
       </c>
       <c r="G150" s="22" t="n">
-        <v>-23.737</v>
+        <v>13.515</v>
       </c>
       <c r="I150" s="22" t="n">
-        <v>-55.13</v>
+        <v>31.282</v>
       </c>
       <c r="K150" s="22" t="n">
-        <v>-17.76</v>
+        <v>18.053</v>
       </c>
       <c r="M150" s="22" t="n">
-        <v>-89.03400000000001</v>
+        <v>43.128</v>
       </c>
       <c r="U150" s="22" t="n">
-        <v>-25.316</v>
+        <v>22.098</v>
       </c>
       <c r="V150" s="22" t="n">
-        <v>-35.692</v>
+        <v>25.472</v>
       </c>
       <c r="W150" s="22" t="n">
-        <v>-55.13</v>
+        <v>31.282</v>
       </c>
       <c r="X150" s="22" t="n">
-        <v>-89.03400000000001</v>
+        <v>43.128</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>자산복구부채 이행 지출</t>
+          <t>보험금 수취</t>
         </is>
       </c>
       <c r="E151" s="22" t="n">
-        <v>0</v>
+        <v>0.589</v>
+      </c>
+      <c r="I151" s="22" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="M151" s="22" t="n">
+        <v>0.461</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>-5.852</v>
+        <v>0.591</v>
       </c>
       <c r="V151" s="22" t="n">
-        <v>0</v>
+        <v>0.589</v>
+      </c>
+      <c r="W151" s="22" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="X151" s="22" t="n">
+        <v>0.461</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="C152" s="22" t="n">
-        <v>0</v>
+        <v>-343.074</v>
       </c>
       <c r="E152" s="22" t="n">
-        <v>0</v>
+        <v>-398.944</v>
       </c>
       <c r="G152" s="22" t="n">
-        <v>-52.322</v>
+        <v>-601.643</v>
       </c>
       <c r="I152" s="22" t="n">
-        <v>-99.548</v>
+        <v>-719.941</v>
       </c>
       <c r="K152" s="22" t="n">
-        <v>-286.481</v>
+        <v>-663.987</v>
       </c>
       <c r="M152" s="22" t="n">
-        <v>-286.503</v>
+        <v>-1104.149</v>
+      </c>
+      <c r="U152" s="22" t="n">
+        <v>-665.624</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>0</v>
+        <v>-398.944</v>
       </c>
       <c r="W152" s="22" t="n">
-        <v>-99.548</v>
+        <v>-719.941</v>
       </c>
       <c r="X152" s="22" t="n">
-        <v>-286.503</v>
+        <v>-1104.149</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
-        </is>
-      </c>
-      <c r="E153" s="22" t="n">
-        <v>0.675</v>
+          <t>법인세 환급</t>
+        </is>
+      </c>
+      <c r="G153" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="I153" s="22" t="n">
-        <v>176.369</v>
+        <v>0</v>
+      </c>
+      <c r="K153" s="22" t="n">
+        <v>40.716</v>
       </c>
       <c r="M153" s="22" t="n">
-        <v>8.843999999999999</v>
-      </c>
-      <c r="U153" s="22" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V153" s="22" t="n">
-        <v>0.675</v>
+        <v>40.716</v>
       </c>
       <c r="W153" s="22" t="n">
-        <v>176.369</v>
+        <v>0</v>
       </c>
       <c r="X153" s="22" t="n">
-        <v>8.843999999999999</v>
+        <v>40.716</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="20" t="inlineStr">
-        <is>
-          <t>사업양도 수입</t>
-        </is>
-      </c>
-      <c r="E154" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U154" s="22" t="n">
-        <v>137.28</v>
-      </c>
-      <c r="V154" s="22" t="n">
-        <v>0</v>
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="n">
+        <v>2482.281</v>
+      </c>
+      <c r="E154" s="12" t="n">
+        <v>1410.295</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>-698.229</v>
+      </c>
+      <c r="I154" s="12" t="n">
+        <v>433.41</v>
+      </c>
+      <c r="K154" s="12" t="n">
+        <v>970.65</v>
+      </c>
+      <c r="M154" s="12" t="n">
+        <v>3872.038</v>
+      </c>
+      <c r="U154" s="12" t="n">
+        <v>616.956</v>
+      </c>
+      <c r="V154" s="12" t="n">
+        <v>1410.295</v>
+      </c>
+      <c r="W154" s="12" t="n">
+        <v>433.41</v>
+      </c>
+      <c r="X154" s="12" t="n">
+        <v>3872.038</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 회수</t>
-        </is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="C155" s="22" t="n">
+        <v>-60.162</v>
       </c>
       <c r="E155" s="22" t="n">
-        <v>0</v>
+        <v>-176.198</v>
+      </c>
+      <c r="G155" s="22" t="n">
+        <v>-149.6</v>
+      </c>
+      <c r="I155" s="22" t="n">
+        <v>-402.524</v>
+      </c>
+      <c r="K155" s="22" t="n">
+        <v>-136.941</v>
+      </c>
+      <c r="M155" s="22" t="n">
+        <v>-270.762</v>
       </c>
       <c r="U155" s="22" t="n">
-        <v>12.845</v>
+        <v>-3750.162</v>
       </c>
       <c r="V155" s="22" t="n">
-        <v>0</v>
+        <v>-176.198</v>
+      </c>
+      <c r="W155" s="22" t="n">
+        <v>-402.524</v>
+      </c>
+      <c r="X155" s="22" t="n">
+        <v>-270.762</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>관계회사 주식 취득</t>
+          <t>유형자산 매각</t>
         </is>
       </c>
       <c r="E156" s="22" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="G156" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I156" s="22" t="n">
-        <v>-124.412</v>
+        <v>0</v>
+      </c>
+      <c r="K156" s="22" t="n">
+        <v>366.389</v>
       </c>
       <c r="M156" s="22" t="n">
+        <v>370.457</v>
+      </c>
+      <c r="U156" s="22" t="n">
+        <v>213.545</v>
+      </c>
+      <c r="V156" s="22" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="W156" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V156" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W156" s="22" t="n">
-        <v>-124.412</v>
-      </c>
       <c r="X156" s="22" t="n">
-        <v>0</v>
+        <v>370.457</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 납입</t>
-        </is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="C157" s="22" t="n">
+        <v>-15.526</v>
       </c>
       <c r="E157" s="22" t="n">
-        <v>0</v>
+        <v>-35.692</v>
+      </c>
+      <c r="G157" s="22" t="n">
+        <v>-23.737</v>
       </c>
       <c r="I157" s="22" t="n">
-        <v>-45.817</v>
+        <v>-55.13</v>
+      </c>
+      <c r="K157" s="22" t="n">
+        <v>-17.76</v>
       </c>
       <c r="M157" s="22" t="n">
-        <v>0</v>
+        <v>-89.03400000000001</v>
+      </c>
+      <c r="U157" s="22" t="n">
+        <v>-25.316</v>
       </c>
       <c r="V157" s="22" t="n">
-        <v>0</v>
+        <v>-35.692</v>
       </c>
       <c r="W157" s="22" t="n">
-        <v>-45.817</v>
+        <v>-55.13</v>
       </c>
       <c r="X157" s="22" t="n">
-        <v>0</v>
+        <v>-89.03400000000001</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C158" s="22" t="n">
-        <v>-1.064</v>
+          <t>자산복구부채 이행 지출</t>
+        </is>
       </c>
       <c r="E158" s="22" t="n">
-        <v>-2.555</v>
-      </c>
-      <c r="G158" s="22" t="n">
-        <v>-3.892</v>
-      </c>
-      <c r="I158" s="22" t="n">
-        <v>-12.575</v>
-      </c>
-      <c r="K158" s="22" t="n">
-        <v>14.132</v>
-      </c>
-      <c r="M158" s="22" t="n">
-        <v>-3.4</v>
+        <v>0</v>
       </c>
       <c r="U158" s="22" t="n">
-        <v>-6.537</v>
+        <v>-5.852</v>
       </c>
       <c r="V158" s="22" t="n">
-        <v>-2.555</v>
-      </c>
-      <c r="W158" s="22" t="n">
-        <v>-12.575</v>
-      </c>
-      <c r="X158" s="22" t="n">
-        <v>-3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C159" s="12" t="n">
-        <v>-76.753</v>
-      </c>
-      <c r="E159" s="12" t="n">
-        <v>-213.561</v>
-      </c>
-      <c r="G159" s="12" t="n">
-        <v>-229.553</v>
-      </c>
-      <c r="I159" s="12" t="n">
-        <v>-563.638</v>
-      </c>
-      <c r="K159" s="12" t="n">
-        <v>-60.661</v>
-      </c>
-      <c r="M159" s="12" t="n">
-        <v>-270.398</v>
-      </c>
-      <c r="U159" s="12" t="n">
-        <v>-3423.798</v>
-      </c>
-      <c r="V159" s="12" t="n">
-        <v>-213.561</v>
-      </c>
-      <c r="W159" s="12" t="n">
-        <v>-563.638</v>
-      </c>
-      <c r="X159" s="12" t="n">
-        <v>-270.398</v>
+      <c r="A159" s="20" t="inlineStr">
+        <is>
+          <t>투자유가증권 취득</t>
+        </is>
+      </c>
+      <c r="C159" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" s="22" t="n">
+        <v>-52.322</v>
+      </c>
+      <c r="I159" s="22" t="n">
+        <v>-99.548</v>
+      </c>
+      <c r="K159" s="22" t="n">
+        <v>-286.481</v>
+      </c>
+      <c r="M159" s="22" t="n">
+        <v>-286.503</v>
+      </c>
+      <c r="V159" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W159" s="22" t="n">
+        <v>-99.548</v>
+      </c>
+      <c r="X159" s="22" t="n">
+        <v>-286.503</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="C160" s="22" t="n">
-        <v>-408.191</v>
+          <t>투자유가증권 매각</t>
+        </is>
       </c>
       <c r="E160" s="22" t="n">
-        <v>-408.83</v>
-      </c>
-      <c r="G160" s="22" t="n">
-        <v>-409.689</v>
+        <v>0.675</v>
       </c>
       <c r="I160" s="22" t="n">
-        <v>-409.689</v>
-      </c>
-      <c r="K160" s="22" t="n">
-        <v>-498.886</v>
+        <v>176.369</v>
       </c>
       <c r="M160" s="22" t="n">
-        <v>-498.958</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="U160" s="22" t="n">
-        <v>-349.873</v>
+        <v>0.4</v>
       </c>
       <c r="V160" s="22" t="n">
-        <v>-408.83</v>
+        <v>0.675</v>
       </c>
       <c r="W160" s="22" t="n">
-        <v>-409.689</v>
+        <v>176.369</v>
       </c>
       <c r="X160" s="22" t="n">
-        <v>-498.958</v>
+        <v>8.843999999999999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C161" s="22" t="n">
-        <v>-0.442</v>
+          <t>사업양도 수입</t>
+        </is>
       </c>
       <c r="E161" s="22" t="n">
-        <v>-0.442</v>
-      </c>
-      <c r="G161" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I161" s="22" t="n">
+      <c r="U161" s="22" t="n">
+        <v>137.28</v>
+      </c>
+      <c r="V161" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="K161" s="22" t="n">
-        <v>-0.264</v>
-      </c>
-      <c r="M161" s="22" t="n">
-        <v>-1.127</v>
-      </c>
-      <c r="U161" s="22" t="n">
-        <v>-0.884</v>
-      </c>
-      <c r="V161" s="22" t="n">
-        <v>-0.442</v>
-      </c>
-      <c r="W161" s="22" t="n">
+    </row>
+    <row r="162">
+      <c r="A162" s="20" t="inlineStr">
+        <is>
+          <t>임차보증금·보증금 회수</t>
+        </is>
+      </c>
+      <c r="E162" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="X161" s="22" t="n">
-        <v>-1.127</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C162" s="12" t="n">
-        <v>-408.633</v>
-      </c>
-      <c r="E162" s="12" t="n">
-        <v>-409.272</v>
-      </c>
-      <c r="G162" s="12" t="n">
-        <v>-409.689</v>
-      </c>
-      <c r="I162" s="12" t="n">
-        <v>-409.689</v>
-      </c>
-      <c r="K162" s="12" t="n">
-        <v>-499.15</v>
-      </c>
-      <c r="M162" s="12" t="n">
-        <v>-500.085</v>
-      </c>
-      <c r="U162" s="12" t="n">
-        <v>-350.757</v>
-      </c>
-      <c r="V162" s="12" t="n">
-        <v>-409.272</v>
-      </c>
-      <c r="W162" s="12" t="n">
-        <v>-409.689</v>
-      </c>
-      <c r="X162" s="12" t="n">
-        <v>-500.085</v>
+      <c r="U162" s="22" t="n">
+        <v>12.845</v>
+      </c>
+      <c r="V162" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
-        </is>
-      </c>
-      <c r="C163" s="22" t="n">
-        <v>0.953</v>
+          <t>관계회사 주식 취득</t>
+        </is>
       </c>
       <c r="E163" s="22" t="n">
-        <v>-1.289</v>
-      </c>
-      <c r="G163" s="22" t="n">
-        <v>-11.964</v>
+        <v>0</v>
       </c>
       <c r="I163" s="22" t="n">
-        <v>-9.989000000000001</v>
-      </c>
-      <c r="K163" s="22" t="n">
-        <v>-6.798</v>
+        <v>-124.412</v>
       </c>
       <c r="M163" s="22" t="n">
-        <v>-4.916</v>
-      </c>
-      <c r="U163" s="22" t="n">
-        <v>1.158</v>
+        <v>0</v>
       </c>
       <c r="V163" s="22" t="n">
-        <v>-1.289</v>
+        <v>0</v>
       </c>
       <c r="W163" s="22" t="n">
-        <v>-9.989000000000001</v>
+        <v>-124.412</v>
       </c>
       <c r="X163" s="22" t="n">
-        <v>-4.916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
+          <t>임차보증금·보증금 납입</t>
+        </is>
+      </c>
+      <c r="E164" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="22" t="n">
+        <v>-45.817</v>
+      </c>
+      <c r="M164" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" s="22" t="n">
+        <v>-45.817</v>
+      </c>
+      <c r="X164" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C165" s="22" t="n">
+        <v>-1.064</v>
+      </c>
+      <c r="E165" s="22" t="n">
+        <v>-2.555</v>
+      </c>
+      <c r="G165" s="22" t="n">
+        <v>-3.892</v>
+      </c>
+      <c r="I165" s="22" t="n">
+        <v>-12.575</v>
+      </c>
+      <c r="K165" s="22" t="n">
+        <v>14.132</v>
+      </c>
+      <c r="M165" s="22" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="U165" s="22" t="n">
+        <v>-6.537</v>
+      </c>
+      <c r="V165" s="22" t="n">
+        <v>-2.555</v>
+      </c>
+      <c r="W165" s="22" t="n">
+        <v>-12.575</v>
+      </c>
+      <c r="X165" s="22" t="n">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C166" s="12" t="n">
+        <v>-76.753</v>
+      </c>
+      <c r="E166" s="12" t="n">
+        <v>-213.561</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>-229.553</v>
+      </c>
+      <c r="I166" s="12" t="n">
+        <v>-563.638</v>
+      </c>
+      <c r="K166" s="12" t="n">
+        <v>-60.661</v>
+      </c>
+      <c r="M166" s="12" t="n">
+        <v>-270.398</v>
+      </c>
+      <c r="U166" s="12" t="n">
+        <v>-3423.798</v>
+      </c>
+      <c r="V166" s="12" t="n">
+        <v>-213.561</v>
+      </c>
+      <c r="W166" s="12" t="n">
+        <v>-563.638</v>
+      </c>
+      <c r="X166" s="12" t="n">
+        <v>-270.398</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="C167" s="22" t="n">
+        <v>-408.191</v>
+      </c>
+      <c r="E167" s="22" t="n">
+        <v>-408.83</v>
+      </c>
+      <c r="G167" s="22" t="n">
+        <v>-409.689</v>
+      </c>
+      <c r="I167" s="22" t="n">
+        <v>-409.689</v>
+      </c>
+      <c r="K167" s="22" t="n">
+        <v>-498.886</v>
+      </c>
+      <c r="M167" s="22" t="n">
+        <v>-498.958</v>
+      </c>
+      <c r="U167" s="22" t="n">
+        <v>-349.873</v>
+      </c>
+      <c r="V167" s="22" t="n">
+        <v>-408.83</v>
+      </c>
+      <c r="W167" s="22" t="n">
+        <v>-409.689</v>
+      </c>
+      <c r="X167" s="22" t="n">
+        <v>-498.958</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C168" s="22" t="n">
+        <v>-0.442</v>
+      </c>
+      <c r="E168" s="22" t="n">
+        <v>-0.442</v>
+      </c>
+      <c r="G168" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" s="22" t="n">
+        <v>-0.264</v>
+      </c>
+      <c r="M168" s="22" t="n">
+        <v>-1.127</v>
+      </c>
+      <c r="U168" s="22" t="n">
+        <v>-0.884</v>
+      </c>
+      <c r="V168" s="22" t="n">
+        <v>-0.442</v>
+      </c>
+      <c r="W168" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X168" s="22" t="n">
+        <v>-1.127</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C169" s="12" t="n">
+        <v>-408.633</v>
+      </c>
+      <c r="E169" s="12" t="n">
+        <v>-409.272</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>-409.689</v>
+      </c>
+      <c r="I169" s="12" t="n">
+        <v>-409.689</v>
+      </c>
+      <c r="K169" s="12" t="n">
+        <v>-499.15</v>
+      </c>
+      <c r="M169" s="12" t="n">
+        <v>-500.085</v>
+      </c>
+      <c r="U169" s="12" t="n">
+        <v>-350.757</v>
+      </c>
+      <c r="V169" s="12" t="n">
+        <v>-409.272</v>
+      </c>
+      <c r="W169" s="12" t="n">
+        <v>-409.689</v>
+      </c>
+      <c r="X169" s="12" t="n">
+        <v>-500.085</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="C170" s="22" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="E170" s="22" t="n">
+        <v>-1.289</v>
+      </c>
+      <c r="G170" s="22" t="n">
+        <v>-11.964</v>
+      </c>
+      <c r="I170" s="22" t="n">
+        <v>-9.989000000000001</v>
+      </c>
+      <c r="K170" s="22" t="n">
+        <v>-6.798</v>
+      </c>
+      <c r="M170" s="22" t="n">
+        <v>-4.916</v>
+      </c>
+      <c r="U170" s="22" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="V170" s="22" t="n">
+        <v>-1.289</v>
+      </c>
+      <c r="W170" s="22" t="n">
+        <v>-9.989000000000001</v>
+      </c>
+      <c r="X170" s="22" t="n">
+        <v>-4.916</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="C164" s="22" t="n">
+      <c r="C171" s="22" t="n">
         <v>1997.848</v>
       </c>
-      <c r="E164" s="22" t="n">
+      <c r="E171" s="22" t="n">
         <v>786.171</v>
       </c>
-      <c r="G164" s="22" t="n">
+      <c r="G171" s="22" t="n">
         <v>-1349.436</v>
       </c>
-      <c r="I164" s="22" t="n">
+      <c r="I171" s="22" t="n">
         <v>-549.907</v>
       </c>
-      <c r="K164" s="22" t="n">
+      <c r="K171" s="22" t="n">
         <v>404.04</v>
       </c>
-      <c r="M164" s="22" t="n">
+      <c r="M171" s="22" t="n">
         <v>3096.637</v>
       </c>
-      <c r="U164" s="22" t="n">
+      <c r="U171" s="22" t="n">
         <v>-3156.44</v>
       </c>
-      <c r="V164" s="22" t="n">
+      <c r="V171" s="22" t="n">
         <v>786.171</v>
       </c>
-      <c r="W164" s="22" t="n">
+      <c r="W171" s="22" t="n">
         <v>-549.907</v>
       </c>
-      <c r="X164" s="22" t="n">
+      <c r="X171" s="22" t="n">
         <v>3096.637</v>
       </c>
     </row>
@@ -9194,7 +9609,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -10479,7 +10894,7 @@
       <c r="K42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -10527,7 +10942,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -10575,7 +10990,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -10623,7 +11038,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -10671,7 +11086,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -10719,7 +11134,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -10767,7 +11182,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -10777,39 +11192,39 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",H28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",I28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",J28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",K28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -10832,7 +11247,7 @@
       <c r="K50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -10880,7 +11295,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -10928,7 +11343,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -10976,7 +11391,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -11024,7 +11439,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -11072,7 +11487,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -11137,7 +11552,7 @@
       <c r="K57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -11185,7 +11600,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -11195,45 +11610,45 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -11243,45 +11658,45 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -11291,45 +11706,45 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -11339,39 +11754,39 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
@@ -11394,7 +11809,7 @@
       <c r="K63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -11442,7 +11857,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -11490,7 +11905,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -11538,7 +11953,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -13667,24 +14082,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
